--- a/2026-KSA-State-League-Timetable.xlsx
+++ b/2026-KSA-State-League-Timetable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Miller\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chrisgraves/Documents/GitHub/KorfballStats2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B29FF60-7977-43C6-A5C8-7FD5508AABE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684D7812-467E-B148-9D3F-DCBF7931B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{34D1CF66-7167-4B48-A765-B822A00030C7}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="23280" windowHeight="14880" xr2:uid="{34D1CF66-7167-4B48-A765-B822A00030C7}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 timetable" sheetId="11" r:id="rId1"/>
@@ -560,16 +560,76 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -578,122 +638,68 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -703,12 +709,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1037,81 +1037,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9D02C9-6900-42C8-B961-4B6E85DA4594}">
   <dimension ref="B1:R119"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="2.5" style="7" customWidth="1"/>
     <col min="2" max="2" width="9" style="7" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="7"/>
-    <col min="5" max="5" width="5.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" style="7"/>
-    <col min="9" max="9" width="2.85546875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="7" customWidth="1"/>
-    <col min="13" max="14" width="8.7109375" style="7"/>
-    <col min="15" max="15" width="2.7109375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="3.7109375" style="7" customWidth="1"/>
-    <col min="17" max="18" width="9.7109375" style="7" customWidth="1"/>
-    <col min="19" max="22" width="8.7109375" style="7"/>
-    <col min="23" max="23" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.7109375" style="7"/>
+    <col min="3" max="3" width="2.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="7"/>
+    <col min="5" max="5" width="5.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="7"/>
+    <col min="9" max="9" width="2.83203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="7" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="7" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="7"/>
+    <col min="15" max="15" width="2.6640625" style="7" customWidth="1"/>
+    <col min="16" max="16" width="3.6640625" style="7" customWidth="1"/>
+    <col min="17" max="18" width="9.6640625" style="7" customWidth="1"/>
+    <col min="19" max="22" width="8.6640625" style="7"/>
+    <col min="23" max="23" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
+    <row r="1" spans="2:18" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-    </row>
-    <row r="3" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+    </row>
+    <row r="3" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="40"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="40"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="30" t="s">
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-    </row>
-    <row r="4" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+    </row>
+    <row r="4" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="49"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="H4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="29"/>
+      <c r="I4" s="40"/>
       <c r="J4" s="9" t="s">
         <v>7</v>
       </c>
@@ -1143,18 +1143,18 @@
       <c r="N4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="29"/>
+      <c r="O4" s="40"/>
       <c r="P4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="Q4" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="30"/>
-    </row>
-    <row r="5" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
+      <c r="R4" s="50"/>
+    </row>
+    <row r="5" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="49"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="25"/>
-      <c r="I5" s="29"/>
+      <c r="I5" s="40"/>
       <c r="J5" s="9">
         <v>1</v>
       </c>
@@ -1180,16 +1180,16 @@
       </c>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
-      <c r="O5" s="29"/>
+      <c r="O5" s="40"/>
       <c r="P5" s="9">
         <v>3</v>
       </c>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="32"/>
-    </row>
-    <row r="6" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="52"/>
+    </row>
+    <row r="6" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="49"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="11">
         <v>0.5</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="25"/>
-      <c r="I6" s="29"/>
+      <c r="I6" s="40"/>
       <c r="J6" s="9">
         <v>1</v>
       </c>
@@ -1215,18 +1215,18 @@
       </c>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
-      <c r="O6" s="29"/>
+      <c r="O6" s="40"/>
       <c r="P6" s="9">
         <v>2</v>
       </c>
-      <c r="Q6" s="33" t="s">
+      <c r="Q6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="34"/>
-    </row>
-    <row r="7" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
+      <c r="R6" s="42"/>
+    </row>
+    <row r="7" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="49"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -1240,71 +1240,71 @@
         <v>28</v>
       </c>
       <c r="H7" s="25"/>
-      <c r="I7" s="29"/>
+      <c r="I7" s="40"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
-      <c r="O7" s="29"/>
+      <c r="O7" s="40"/>
       <c r="P7" s="9">
         <v>1</v>
       </c>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="32"/>
-    </row>
-    <row r="8" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
+      <c r="Q7" s="51"/>
+      <c r="R7" s="52"/>
+    </row>
+    <row r="8" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-    </row>
-    <row r="10" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+    </row>
+    <row r="10" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="29"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="40"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30" t="s">
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-    </row>
-    <row r="11" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+    </row>
+    <row r="11" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="49"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="9" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="H11" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="29"/>
+      <c r="I11" s="40"/>
       <c r="J11" s="9" t="s">
         <v>7</v>
       </c>
@@ -1336,18 +1336,18 @@
       <c r="N11" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O11" s="29"/>
+      <c r="O11" s="40"/>
       <c r="P11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="Q11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R11" s="30"/>
-    </row>
-    <row r="12" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
+      <c r="R11" s="50"/>
+    </row>
+    <row r="12" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="49"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="25"/>
-      <c r="I12" s="29"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="9">
         <v>1</v>
       </c>
@@ -1373,16 +1373,16 @@
       </c>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
-      <c r="O12" s="29"/>
+      <c r="O12" s="40"/>
       <c r="P12" s="9">
         <v>3</v>
       </c>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="32"/>
-    </row>
-    <row r="13" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="52"/>
+    </row>
+    <row r="13" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="49"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="11">
         <v>0.5</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>46</v>
       </c>
       <c r="H13" s="25"/>
-      <c r="I13" s="29"/>
+      <c r="I13" s="40"/>
       <c r="J13" s="9">
         <v>1</v>
       </c>
@@ -1408,18 +1408,18 @@
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
-      <c r="O13" s="29"/>
+      <c r="O13" s="40"/>
       <c r="P13" s="9">
         <v>2</v>
       </c>
-      <c r="Q13" s="33" t="s">
+      <c r="Q13" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="34"/>
-    </row>
-    <row r="14" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
+      <c r="R13" s="42"/>
+    </row>
+    <row r="14" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="49"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -1433,71 +1433,71 @@
         <v>13</v>
       </c>
       <c r="H14" s="25"/>
-      <c r="I14" s="29"/>
+      <c r="I14" s="40"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="25"/>
       <c r="N14" s="25"/>
-      <c r="O14" s="29"/>
+      <c r="O14" s="40"/>
       <c r="P14" s="9">
         <v>1</v>
       </c>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="32"/>
-    </row>
-    <row r="15" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
+      <c r="Q14" s="51"/>
+      <c r="R14" s="52"/>
+    </row>
+    <row r="15" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-    </row>
-    <row r="17" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+    </row>
+    <row r="17" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="29"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="29"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="30" t="s">
+      <c r="K17" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="30" t="s">
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-    </row>
-    <row r="18" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50"/>
+    </row>
+    <row r="18" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="49"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="9" t="s">
         <v>8</v>
       </c>
@@ -1513,7 +1513,7 @@
       <c r="H18" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="29"/>
+      <c r="I18" s="40"/>
       <c r="J18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1529,18 +1529,18 @@
       <c r="N18" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="29"/>
+      <c r="O18" s="40"/>
       <c r="P18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q18" s="30" t="s">
+      <c r="Q18" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R18" s="30"/>
-    </row>
-    <row r="19" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
+      <c r="R18" s="50"/>
+    </row>
+    <row r="19" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="49"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>13</v>
       </c>
       <c r="H19" s="9"/>
-      <c r="I19" s="29"/>
+      <c r="I19" s="40"/>
       <c r="J19" s="9">
         <v>1</v>
       </c>
@@ -1566,16 +1566,16 @@
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="29"/>
+      <c r="O19" s="40"/>
       <c r="P19" s="9">
         <v>3</v>
       </c>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="32"/>
-    </row>
-    <row r="20" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="52"/>
+    </row>
+    <row r="20" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="49"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="11">
         <v>0.5</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="9"/>
-      <c r="I20" s="29"/>
+      <c r="I20" s="40"/>
       <c r="J20" s="9">
         <v>1</v>
       </c>
@@ -1601,18 +1601,18 @@
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="29"/>
+      <c r="O20" s="40"/>
       <c r="P20" s="9">
         <v>2</v>
       </c>
-      <c r="Q20" s="33" t="s">
+      <c r="Q20" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="34"/>
-    </row>
-    <row r="21" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
+      <c r="R20" s="42"/>
+    </row>
+    <row r="21" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="49"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -1626,97 +1626,97 @@
         <v>14</v>
       </c>
       <c r="H21" s="9"/>
-      <c r="I21" s="29"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="29"/>
+      <c r="O21" s="40"/>
       <c r="P21" s="9">
         <v>1</v>
       </c>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="32"/>
-    </row>
-    <row r="22" spans="2:18" s="10" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="51"/>
+      <c r="R21" s="52"/>
+    </row>
+    <row r="22" spans="2:18" s="10" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
     </row>
-    <row r="23" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="35" t="s">
+    <row r="23" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-    </row>
-    <row r="24" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+    </row>
+    <row r="24" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-    </row>
-    <row r="26" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="36" t="s">
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+    </row>
+    <row r="26" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="29"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="29"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="40"/>
       <c r="J26" s="9"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="30" t="s">
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-    </row>
-    <row r="27" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="36"/>
-      <c r="C27" s="29"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+    </row>
+    <row r="27" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="67"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="9" t="s">
         <v>8</v>
       </c>
@@ -1732,7 +1732,7 @@
       <c r="H27" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I27" s="29"/>
+      <c r="I27" s="40"/>
       <c r="J27" s="9" t="s">
         <v>7</v>
       </c>
@@ -1748,18 +1748,18 @@
       <c r="N27" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="29"/>
+      <c r="O27" s="40"/>
       <c r="P27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q27" s="30" t="s">
+      <c r="Q27" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="30"/>
-    </row>
-    <row r="28" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="36"/>
-      <c r="C28" s="29"/>
+      <c r="R27" s="50"/>
+    </row>
+    <row r="28" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="67"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="11">
         <v>0.52083333333333337</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>14</v>
       </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="29"/>
+      <c r="I28" s="40"/>
       <c r="J28" s="9">
         <v>1</v>
       </c>
@@ -1785,16 +1785,16 @@
       </c>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="29"/>
+      <c r="O28" s="40"/>
       <c r="P28" s="9">
         <v>3</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="32"/>
-    </row>
-    <row r="29" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="36"/>
-      <c r="C29" s="29"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="52"/>
+    </row>
+    <row r="29" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="67"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="11">
         <v>0.57291666666666663</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="H29" s="9"/>
-      <c r="I29" s="29"/>
+      <c r="I29" s="40"/>
       <c r="J29" s="9">
         <v>1</v>
       </c>
@@ -1820,18 +1820,18 @@
       </c>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="29"/>
+      <c r="O29" s="40"/>
       <c r="P29" s="9">
         <v>2</v>
       </c>
-      <c r="Q29" s="33" t="s">
+      <c r="Q29" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="R29" s="34"/>
-    </row>
-    <row r="30" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="36"/>
-      <c r="C30" s="29"/>
+      <c r="R29" s="42"/>
+    </row>
+    <row r="30" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="67"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="11">
         <v>0.625</v>
       </c>
@@ -1845,71 +1845,71 @@
         <v>28</v>
       </c>
       <c r="H30" s="9"/>
-      <c r="I30" s="29"/>
+      <c r="I30" s="40"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="29"/>
+      <c r="O30" s="40"/>
       <c r="P30" s="9">
         <v>1</v>
       </c>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="32"/>
-    </row>
-    <row r="31" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="27" t="s">
+      <c r="Q30" s="51"/>
+      <c r="R30" s="52"/>
+    </row>
+    <row r="31" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-    </row>
-    <row r="33" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="36" t="s">
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+    </row>
+    <row r="33" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="29"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="29"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="40"/>
       <c r="J33" s="9"/>
-      <c r="K33" s="30" t="s">
+      <c r="K33" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="30" t="s">
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-    </row>
-    <row r="34" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="36"/>
-      <c r="C34" s="29"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+    </row>
+    <row r="34" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="67"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="9" t="s">
         <v>8</v>
       </c>
@@ -1925,7 +1925,7 @@
       <c r="H34" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I34" s="29"/>
+      <c r="I34" s="40"/>
       <c r="J34" s="9" t="s">
         <v>7</v>
       </c>
@@ -1941,18 +1941,18 @@
       <c r="N34" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O34" s="29"/>
+      <c r="O34" s="40"/>
       <c r="P34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q34" s="30" t="s">
+      <c r="Q34" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R34" s="30"/>
-    </row>
-    <row r="35" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="36"/>
-      <c r="C35" s="29"/>
+      <c r="R34" s="50"/>
+    </row>
+    <row r="35" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="67"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="11">
         <v>0.52083333333333337</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="H35" s="9"/>
-      <c r="I35" s="29"/>
+      <c r="I35" s="40"/>
       <c r="J35" s="9">
         <v>1</v>
       </c>
@@ -1978,16 +1978,16 @@
       </c>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="29"/>
+      <c r="O35" s="40"/>
       <c r="P35" s="9">
         <v>3</v>
       </c>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="32"/>
-    </row>
-    <row r="36" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="36"/>
-      <c r="C36" s="29"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="52"/>
+    </row>
+    <row r="36" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="67"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="11">
         <v>0.57291666666666663</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>28</v>
       </c>
       <c r="H36" s="9"/>
-      <c r="I36" s="29"/>
+      <c r="I36" s="40"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -2013,18 +2013,18 @@
       </c>
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="29"/>
+      <c r="O36" s="40"/>
       <c r="P36" s="9">
         <v>2</v>
       </c>
-      <c r="Q36" s="33" t="s">
+      <c r="Q36" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="R36" s="34"/>
-    </row>
-    <row r="37" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
-      <c r="C37" s="29"/>
+      <c r="R36" s="42"/>
+    </row>
+    <row r="37" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="67"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="11">
         <v>0.625</v>
       </c>
@@ -2038,71 +2038,71 @@
         <v>6</v>
       </c>
       <c r="H37" s="9"/>
-      <c r="I37" s="29"/>
+      <c r="I37" s="40"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
-      <c r="O37" s="29"/>
+      <c r="O37" s="40"/>
       <c r="P37" s="9">
         <v>1</v>
       </c>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="32"/>
-    </row>
-    <row r="38" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="27" t="s">
+      <c r="Q37" s="51"/>
+      <c r="R37" s="52"/>
+    </row>
+    <row r="38" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-    </row>
-    <row r="40" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="36" t="s">
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+    </row>
+    <row r="40" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="29"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="29"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="40"/>
       <c r="J40" s="9"/>
-      <c r="K40" s="30" t="s">
+      <c r="K40" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="30" t="s">
+      <c r="L40" s="50"/>
+      <c r="M40" s="50"/>
+      <c r="N40" s="50"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-    </row>
-    <row r="41" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="36"/>
-      <c r="C41" s="29"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50"/>
+    </row>
+    <row r="41" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="67"/>
+      <c r="C41" s="40"/>
       <c r="D41" s="9" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="H41" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I41" s="29"/>
+      <c r="I41" s="40"/>
       <c r="J41" s="9" t="s">
         <v>7</v>
       </c>
@@ -2134,18 +2134,18 @@
       <c r="N41" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="29"/>
+      <c r="O41" s="40"/>
       <c r="P41" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q41" s="30" t="s">
+      <c r="Q41" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R41" s="30"/>
-    </row>
-    <row r="42" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="36"/>
-      <c r="C42" s="29"/>
+      <c r="R41" s="50"/>
+    </row>
+    <row r="42" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="67"/>
+      <c r="C42" s="40"/>
       <c r="D42" s="11">
         <v>0.52083333333333337</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>15</v>
       </c>
       <c r="H42" s="9"/>
-      <c r="I42" s="29"/>
+      <c r="I42" s="40"/>
       <c r="J42" s="9">
         <v>1</v>
       </c>
@@ -2171,16 +2171,16 @@
       </c>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
-      <c r="O42" s="29"/>
+      <c r="O42" s="40"/>
       <c r="P42" s="9">
         <v>3</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="32"/>
-    </row>
-    <row r="43" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="36"/>
-      <c r="C43" s="29"/>
+      <c r="Q42" s="51"/>
+      <c r="R42" s="52"/>
+    </row>
+    <row r="43" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="67"/>
+      <c r="C43" s="40"/>
       <c r="D43" s="11">
         <v>0.57291666666666663</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>6</v>
       </c>
       <c r="H43" s="9"/>
-      <c r="I43" s="29"/>
+      <c r="I43" s="40"/>
       <c r="J43" s="9">
         <v>1</v>
       </c>
@@ -2206,18 +2206,18 @@
       </c>
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
-      <c r="O43" s="29"/>
+      <c r="O43" s="40"/>
       <c r="P43" s="9">
         <v>2</v>
       </c>
-      <c r="Q43" s="33" t="s">
+      <c r="Q43" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="R43" s="34"/>
-    </row>
-    <row r="44" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="36"/>
-      <c r="C44" s="29"/>
+      <c r="R43" s="42"/>
+    </row>
+    <row r="44" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="67"/>
+      <c r="C44" s="40"/>
       <c r="D44" s="11">
         <v>0.625</v>
       </c>
@@ -2231,71 +2231,71 @@
         <v>16</v>
       </c>
       <c r="H44" s="9"/>
-      <c r="I44" s="29"/>
+      <c r="I44" s="40"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
-      <c r="O44" s="29"/>
+      <c r="O44" s="40"/>
       <c r="P44" s="9">
         <v>1</v>
       </c>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="34"/>
-    </row>
-    <row r="45" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="27" t="s">
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
+    </row>
+    <row r="45" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-    </row>
-    <row r="47" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="36" t="s">
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+    </row>
+    <row r="47" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="37"/>
+      <c r="C47" s="68"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
-      <c r="F47" s="40" t="s">
+      <c r="F47" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="G47" s="41"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="29"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="40"/>
       <c r="J47" s="9"/>
-      <c r="K47" s="40" t="s">
+      <c r="K47" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="42"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="40" t="s">
+      <c r="L47" s="71"/>
+      <c r="M47" s="71"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="42"/>
-    </row>
-    <row r="48" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="36"/>
-      <c r="C48" s="38"/>
+      <c r="Q47" s="71"/>
+      <c r="R47" s="54"/>
+    </row>
+    <row r="48" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="67"/>
+      <c r="C48" s="69"/>
       <c r="D48" s="9" t="s">
         <v>8</v>
       </c>
@@ -2311,7 +2311,7 @@
       <c r="H48" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I48" s="29"/>
+      <c r="I48" s="40"/>
       <c r="J48" s="9" t="s">
         <v>7</v>
       </c>
@@ -2327,18 +2327,18 @@
       <c r="N48" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="29"/>
+      <c r="O48" s="40"/>
       <c r="P48" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q48" s="30" t="s">
+      <c r="Q48" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R48" s="30"/>
-    </row>
-    <row r="49" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="36"/>
-      <c r="C49" s="38"/>
+      <c r="R48" s="50"/>
+    </row>
+    <row r="49" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="67"/>
+      <c r="C49" s="69"/>
       <c r="D49" s="11">
         <v>0.52083333333333337</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="9"/>
-      <c r="I49" s="29"/>
+      <c r="I49" s="40"/>
       <c r="J49" s="9">
         <v>1</v>
       </c>
@@ -2364,16 +2364,16 @@
       </c>
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
-      <c r="O49" s="29"/>
+      <c r="O49" s="40"/>
       <c r="P49" s="9">
         <v>3</v>
       </c>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="32"/>
-    </row>
-    <row r="50" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="36"/>
-      <c r="C50" s="38"/>
+      <c r="Q49" s="51"/>
+      <c r="R49" s="52"/>
+    </row>
+    <row r="50" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="67"/>
+      <c r="C50" s="69"/>
       <c r="D50" s="11">
         <v>0.57291666666666663</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>13</v>
       </c>
       <c r="H50" s="9"/>
-      <c r="I50" s="29"/>
+      <c r="I50" s="40"/>
       <c r="J50" s="9">
         <v>1</v>
       </c>
@@ -2399,18 +2399,18 @@
       </c>
       <c r="M50" s="9"/>
       <c r="N50" s="9"/>
-      <c r="O50" s="29"/>
+      <c r="O50" s="40"/>
       <c r="P50" s="9">
         <v>2</v>
       </c>
-      <c r="Q50" s="33" t="s">
+      <c r="Q50" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="R50" s="34"/>
-    </row>
-    <row r="51" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="36"/>
-      <c r="C51" s="39"/>
+      <c r="R50" s="42"/>
+    </row>
+    <row r="51" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="67"/>
+      <c r="C51" s="70"/>
       <c r="D51" s="11">
         <v>0.625</v>
       </c>
@@ -2424,70 +2424,70 @@
         <v>28</v>
       </c>
       <c r="H51" s="9"/>
-      <c r="I51" s="29"/>
+      <c r="I51" s="40"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
       <c r="N51" s="9"/>
-      <c r="O51" s="29"/>
+      <c r="O51" s="40"/>
       <c r="P51" s="9">
         <v>1</v>
       </c>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34"/>
-    </row>
-    <row r="52" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="27" t="s">
+      <c r="Q51" s="41"/>
+      <c r="R51" s="42"/>
+    </row>
+    <row r="52" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
-      <c r="O53" s="27"/>
-      <c r="P53" s="27"/>
-      <c r="Q53" s="27"/>
-      <c r="R53" s="27"/>
-    </row>
-    <row r="54" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="28" t="s">
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="28"/>
+      <c r="P53" s="28"/>
+      <c r="Q53" s="28"/>
+      <c r="R53" s="28"/>
+    </row>
+    <row r="54" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="49" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="29"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="40"/>
       <c r="J54" s="9"/>
-      <c r="K54" s="30" t="s">
+      <c r="K54" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
+      <c r="L54" s="50"/>
+      <c r="M54" s="50"/>
+      <c r="N54" s="50"/>
       <c r="O54" s="14"/>
-      <c r="P54" s="46" t="s">
+      <c r="P54" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="46"/>
-      <c r="R54" s="46"/>
-    </row>
-    <row r="55" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="28"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+    </row>
+    <row r="55" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="49"/>
       <c r="C55" s="44"/>
       <c r="D55" s="9" t="s">
         <v>8</v>
@@ -2504,7 +2504,7 @@
       <c r="H55" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I55" s="29"/>
+      <c r="I55" s="40"/>
       <c r="J55" s="9" t="s">
         <v>7</v>
       </c>
@@ -2524,13 +2524,13 @@
       <c r="P55" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q55" s="30" t="s">
+      <c r="Q55" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R55" s="30"/>
-    </row>
-    <row r="56" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="28"/>
+      <c r="R55" s="50"/>
+    </row>
+    <row r="56" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="49"/>
       <c r="C56" s="44"/>
       <c r="D56" s="11">
         <v>0.44791666666666669</v>
@@ -2538,10 +2538,10 @@
       <c r="E56" s="9">
         <v>2</v>
       </c>
-      <c r="F56" s="50"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="29"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="60"/>
+      <c r="I56" s="40"/>
       <c r="J56" s="9">
         <v>1</v>
       </c>
@@ -2555,11 +2555,11 @@
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="32"/>
-    </row>
-    <row r="57" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="28"/>
+      <c r="Q56" s="51"/>
+      <c r="R56" s="52"/>
+    </row>
+    <row r="57" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="49"/>
       <c r="C57" s="44"/>
       <c r="D57" s="11">
         <v>0.5</v>
@@ -2567,10 +2567,10 @@
       <c r="E57" s="9">
         <v>2</v>
       </c>
-      <c r="F57" s="53"/>
-      <c r="G57" s="54"/>
-      <c r="H57" s="55"/>
-      <c r="I57" s="29"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="40"/>
       <c r="J57" s="9">
         <v>1</v>
       </c>
@@ -2586,13 +2586,13 @@
       <c r="P57" s="9">
         <v>2</v>
       </c>
-      <c r="Q57" s="33" t="s">
+      <c r="Q57" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="R57" s="34"/>
-    </row>
-    <row r="58" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="28"/>
+      <c r="R57" s="42"/>
+    </row>
+    <row r="58" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="49"/>
       <c r="C58" s="45"/>
       <c r="D58" s="11">
         <v>0.55208333333333337</v>
@@ -2600,10 +2600,10 @@
       <c r="E58" s="9">
         <v>2</v>
       </c>
-      <c r="F58" s="56"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="29"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="40"/>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
@@ -2613,61 +2613,61 @@
       <c r="P58" s="9">
         <v>1</v>
       </c>
-      <c r="Q58" s="33"/>
-      <c r="R58" s="34"/>
-    </row>
-    <row r="59" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="27" t="s">
+      <c r="Q58" s="41"/>
+      <c r="R58" s="42"/>
+    </row>
+    <row r="59" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-    </row>
-    <row r="61" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="28" t="s">
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+      <c r="P60" s="28"/>
+      <c r="Q60" s="28"/>
+      <c r="R60" s="28"/>
+    </row>
+    <row r="61" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="47"/>
+      <c r="C61" s="55"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
-      <c r="F61" s="30" t="s">
+      <c r="F61" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="29"/>
+      <c r="G61" s="50"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="40"/>
       <c r="J61" s="9"/>
-      <c r="K61" s="30" t="s">
+      <c r="K61" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="30" t="s">
+      <c r="L61" s="50"/>
+      <c r="M61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="40"/>
+      <c r="P61" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-    </row>
-    <row r="62" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="28"/>
-      <c r="C62" s="48"/>
+      <c r="Q61" s="50"/>
+      <c r="R61" s="50"/>
+    </row>
+    <row r="62" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="49"/>
+      <c r="C62" s="56"/>
       <c r="D62" s="9" t="s">
         <v>8</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="H62" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I62" s="29"/>
+      <c r="I62" s="40"/>
       <c r="J62" s="9" t="s">
         <v>7</v>
       </c>
@@ -2699,18 +2699,18 @@
       <c r="N62" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="29"/>
+      <c r="O62" s="40"/>
       <c r="P62" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q62" s="30" t="s">
+      <c r="Q62" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R62" s="30"/>
-    </row>
-    <row r="63" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="28"/>
-      <c r="C63" s="48"/>
+      <c r="R62" s="50"/>
+    </row>
+    <row r="63" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="49"/>
+      <c r="C63" s="56"/>
       <c r="D63" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>46</v>
       </c>
       <c r="H63" s="25"/>
-      <c r="I63" s="29"/>
+      <c r="I63" s="40"/>
       <c r="J63" s="9">
         <v>1</v>
       </c>
@@ -2736,16 +2736,16 @@
       </c>
       <c r="M63" s="25"/>
       <c r="N63" s="25"/>
-      <c r="O63" s="29"/>
+      <c r="O63" s="40"/>
       <c r="P63" s="9">
         <v>3</v>
       </c>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="32"/>
-    </row>
-    <row r="64" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="28"/>
-      <c r="C64" s="48"/>
+      <c r="Q63" s="51"/>
+      <c r="R63" s="52"/>
+    </row>
+    <row r="64" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="49"/>
+      <c r="C64" s="56"/>
       <c r="D64" s="11">
         <v>0.5</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>6</v>
       </c>
       <c r="H64" s="25"/>
-      <c r="I64" s="29"/>
+      <c r="I64" s="40"/>
       <c r="J64" s="9">
         <v>1</v>
       </c>
@@ -2771,18 +2771,18 @@
       </c>
       <c r="M64" s="25"/>
       <c r="N64" s="25"/>
-      <c r="O64" s="29"/>
+      <c r="O64" s="40"/>
       <c r="P64" s="9">
         <v>2</v>
       </c>
-      <c r="Q64" s="33" t="s">
+      <c r="Q64" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="R64" s="34"/>
-    </row>
-    <row r="65" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="28"/>
-      <c r="C65" s="49"/>
+      <c r="R64" s="42"/>
+    </row>
+    <row r="65" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="49"/>
+      <c r="C65" s="57"/>
       <c r="D65" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -2796,71 +2796,71 @@
         <v>14</v>
       </c>
       <c r="H65" s="25"/>
-      <c r="I65" s="29"/>
+      <c r="I65" s="40"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
       <c r="L65" s="9"/>
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
-      <c r="O65" s="29"/>
+      <c r="O65" s="40"/>
       <c r="P65" s="9">
         <v>1</v>
       </c>
-      <c r="Q65" s="33"/>
-      <c r="R65" s="34"/>
-    </row>
-    <row r="66" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="27" t="s">
+      <c r="Q65" s="41"/>
+      <c r="R65" s="42"/>
+    </row>
+    <row r="66" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-    </row>
-    <row r="68" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="28" t="s">
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+    </row>
+    <row r="68" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="29"/>
+      <c r="C68" s="40"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
-      <c r="F68" s="30" t="s">
+      <c r="F68" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="29"/>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="40"/>
       <c r="J68" s="9"/>
-      <c r="K68" s="30" t="s">
+      <c r="K68" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L68" s="30"/>
-      <c r="M68" s="30"/>
-      <c r="N68" s="30"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="30" t="s">
+      <c r="L68" s="50"/>
+      <c r="M68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="40"/>
+      <c r="P68" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q68" s="30"/>
-      <c r="R68" s="30"/>
-    </row>
-    <row r="69" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="28"/>
-      <c r="C69" s="29"/>
+      <c r="Q68" s="50"/>
+      <c r="R68" s="50"/>
+    </row>
+    <row r="69" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="49"/>
+      <c r="C69" s="40"/>
       <c r="D69" s="9" t="s">
         <v>8</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="H69" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I69" s="29"/>
+      <c r="I69" s="40"/>
       <c r="J69" s="9" t="s">
         <v>7</v>
       </c>
@@ -2892,18 +2892,18 @@
       <c r="N69" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O69" s="29"/>
+      <c r="O69" s="40"/>
       <c r="P69" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q69" s="30" t="s">
+      <c r="Q69" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R69" s="30"/>
-    </row>
-    <row r="70" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="28"/>
-      <c r="C70" s="29"/>
+      <c r="R69" s="50"/>
+    </row>
+    <row r="70" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="49"/>
+      <c r="C70" s="40"/>
       <c r="D70" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>15</v>
       </c>
       <c r="H70" s="25"/>
-      <c r="I70" s="29"/>
+      <c r="I70" s="40"/>
       <c r="J70" s="9">
         <v>2</v>
       </c>
@@ -2928,17 +2928,17 @@
         <v>6</v>
       </c>
       <c r="M70" s="25"/>
-      <c r="N70" s="76"/>
-      <c r="O70" s="29"/>
+      <c r="N70" s="27"/>
+      <c r="O70" s="40"/>
       <c r="P70" s="9">
         <v>3</v>
       </c>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="32"/>
-    </row>
-    <row r="71" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="28"/>
-      <c r="C71" s="29"/>
+      <c r="Q70" s="51"/>
+      <c r="R70" s="52"/>
+    </row>
+    <row r="71" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="49"/>
+      <c r="C71" s="40"/>
       <c r="D71" s="11">
         <v>0.5</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="H71" s="25"/>
-      <c r="I71" s="29"/>
+      <c r="I71" s="40"/>
       <c r="J71" s="9">
         <v>1</v>
       </c>
@@ -2964,18 +2964,18 @@
       </c>
       <c r="M71" s="25"/>
       <c r="N71" s="25"/>
-      <c r="O71" s="29"/>
+      <c r="O71" s="40"/>
       <c r="P71" s="9">
         <v>2</v>
       </c>
-      <c r="Q71" s="33" t="s">
+      <c r="Q71" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="R71" s="34"/>
-    </row>
-    <row r="72" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="28"/>
-      <c r="C72" s="29"/>
+      <c r="R71" s="42"/>
+    </row>
+    <row r="72" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="49"/>
+      <c r="C72" s="40"/>
       <c r="D72" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -2983,8 +2983,10 @@
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="25"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="9"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="9">
+        <v>1</v>
+      </c>
       <c r="K72" s="9" t="s">
         <v>16</v>
       </c>
@@ -2993,65 +2995,65 @@
       </c>
       <c r="M72" s="25"/>
       <c r="N72" s="25"/>
-      <c r="O72" s="29"/>
+      <c r="O72" s="40"/>
       <c r="P72" s="9">
         <v>1</v>
       </c>
-      <c r="Q72" s="33"/>
-      <c r="R72" s="34"/>
-    </row>
-    <row r="73" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="27" t="s">
+      <c r="Q72" s="41"/>
+      <c r="R72" s="42"/>
+    </row>
+    <row r="73" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27"/>
-      <c r="O74" s="27"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="27"/>
-      <c r="R74" s="27"/>
-    </row>
-    <row r="75" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="28" t="s">
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="28"/>
+      <c r="L74" s="28"/>
+      <c r="M74" s="28"/>
+      <c r="N74" s="28"/>
+      <c r="O74" s="28"/>
+      <c r="P74" s="28"/>
+      <c r="Q74" s="28"/>
+      <c r="R74" s="28"/>
+    </row>
+    <row r="75" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="29"/>
+      <c r="C75" s="40"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
-      <c r="F75" s="30" t="s">
+      <c r="F75" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="29"/>
+      <c r="G75" s="50"/>
+      <c r="H75" s="50"/>
+      <c r="I75" s="40"/>
       <c r="J75" s="9"/>
-      <c r="K75" s="30" t="s">
+      <c r="K75" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="L75" s="30"/>
-      <c r="M75" s="30"/>
-      <c r="N75" s="30"/>
-      <c r="O75" s="29"/>
-      <c r="P75" s="30" t="s">
+      <c r="L75" s="50"/>
+      <c r="M75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="40"/>
+      <c r="P75" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q75" s="30"/>
-      <c r="R75" s="30"/>
-    </row>
-    <row r="76" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="28"/>
-      <c r="C76" s="29"/>
+      <c r="Q75" s="50"/>
+      <c r="R75" s="50"/>
+    </row>
+    <row r="76" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="49"/>
+      <c r="C76" s="40"/>
       <c r="D76" s="9" t="s">
         <v>8</v>
       </c>
@@ -3067,7 +3069,7 @@
       <c r="H76" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I76" s="29"/>
+      <c r="I76" s="40"/>
       <c r="J76" s="9" t="s">
         <v>7</v>
       </c>
@@ -3083,18 +3085,18 @@
       <c r="N76" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="29"/>
+      <c r="O76" s="40"/>
       <c r="P76" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q76" s="30" t="s">
+      <c r="Q76" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R76" s="30"/>
-    </row>
-    <row r="77" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="28"/>
-      <c r="C77" s="29"/>
+      <c r="R76" s="50"/>
+    </row>
+    <row r="77" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="49"/>
+      <c r="C77" s="40"/>
       <c r="D77" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -3108,7 +3110,7 @@
         <v>46</v>
       </c>
       <c r="H77" s="25"/>
-      <c r="I77" s="29"/>
+      <c r="I77" s="40"/>
       <c r="J77" s="9">
         <v>1</v>
       </c>
@@ -3120,16 +3122,16 @@
       </c>
       <c r="M77" s="25"/>
       <c r="N77" s="25"/>
-      <c r="O77" s="29"/>
+      <c r="O77" s="40"/>
       <c r="P77" s="9">
         <v>3</v>
       </c>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="32"/>
-    </row>
-    <row r="78" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="28"/>
-      <c r="C78" s="29"/>
+      <c r="Q77" s="51"/>
+      <c r="R77" s="52"/>
+    </row>
+    <row r="78" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="49"/>
+      <c r="C78" s="40"/>
       <c r="D78" s="11">
         <v>0.5</v>
       </c>
@@ -3143,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="H78" s="25"/>
-      <c r="I78" s="29"/>
+      <c r="I78" s="40"/>
       <c r="J78" s="9">
         <v>1</v>
       </c>
@@ -3155,18 +3157,18 @@
       </c>
       <c r="M78" s="25"/>
       <c r="N78" s="25"/>
-      <c r="O78" s="29"/>
+      <c r="O78" s="40"/>
       <c r="P78" s="9">
         <v>2</v>
       </c>
-      <c r="Q78" s="33" t="s">
+      <c r="Q78" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R78" s="34"/>
-    </row>
-    <row r="79" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="28"/>
-      <c r="C79" s="29"/>
+      <c r="R78" s="42"/>
+    </row>
+    <row r="79" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="49"/>
+      <c r="C79" s="40"/>
       <c r="D79" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -3180,71 +3182,71 @@
         <v>16</v>
       </c>
       <c r="H79" s="25"/>
-      <c r="I79" s="29"/>
+      <c r="I79" s="40"/>
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
       <c r="M79" s="25"/>
       <c r="N79" s="25"/>
-      <c r="O79" s="29"/>
+      <c r="O79" s="40"/>
       <c r="P79" s="9">
         <v>1</v>
       </c>
-      <c r="Q79" s="33"/>
-      <c r="R79" s="34"/>
-    </row>
-    <row r="80" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="27" t="s">
+      <c r="Q79" s="41"/>
+      <c r="R79" s="42"/>
+    </row>
+    <row r="80" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-      <c r="M81" s="27"/>
-      <c r="N81" s="27"/>
-      <c r="O81" s="27"/>
-      <c r="P81" s="27"/>
-      <c r="Q81" s="27"/>
-      <c r="R81" s="27"/>
-    </row>
-    <row r="82" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="28" t="s">
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="28"/>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+    </row>
+    <row r="82" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="29"/>
+      <c r="C82" s="40"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
-      <c r="F82" s="30" t="s">
+      <c r="F82" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="29"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="40"/>
       <c r="J82" s="9"/>
-      <c r="K82" s="30" t="s">
+      <c r="K82" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="L82" s="30"/>
-      <c r="M82" s="30"/>
-      <c r="N82" s="30"/>
-      <c r="O82" s="29"/>
-      <c r="P82" s="30" t="s">
+      <c r="L82" s="50"/>
+      <c r="M82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="40"/>
+      <c r="P82" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q82" s="30"/>
-      <c r="R82" s="30"/>
-    </row>
-    <row r="83" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="28"/>
-      <c r="C83" s="29"/>
+      <c r="Q82" s="50"/>
+      <c r="R82" s="50"/>
+    </row>
+    <row r="83" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="49"/>
+      <c r="C83" s="40"/>
       <c r="D83" s="9" t="s">
         <v>8</v>
       </c>
@@ -3260,7 +3262,7 @@
       <c r="H83" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I83" s="29"/>
+      <c r="I83" s="40"/>
       <c r="J83" s="9" t="s">
         <v>7</v>
       </c>
@@ -3276,18 +3278,18 @@
       <c r="N83" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="29"/>
+      <c r="O83" s="40"/>
       <c r="P83" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q83" s="30" t="s">
+      <c r="Q83" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R83" s="30"/>
-    </row>
-    <row r="84" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="28"/>
-      <c r="C84" s="29"/>
+      <c r="R83" s="50"/>
+    </row>
+    <row r="84" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="49"/>
+      <c r="C84" s="40"/>
       <c r="D84" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -3301,7 +3303,7 @@
         <v>46</v>
       </c>
       <c r="H84" s="25"/>
-      <c r="I84" s="29"/>
+      <c r="I84" s="40"/>
       <c r="J84" s="9">
         <v>1</v>
       </c>
@@ -3313,16 +3315,16 @@
       </c>
       <c r="M84" s="25"/>
       <c r="N84" s="25"/>
-      <c r="O84" s="29"/>
+      <c r="O84" s="40"/>
       <c r="P84" s="9">
         <v>3</v>
       </c>
-      <c r="Q84" s="31"/>
-      <c r="R84" s="32"/>
-    </row>
-    <row r="85" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="28"/>
-      <c r="C85" s="29"/>
+      <c r="Q84" s="51"/>
+      <c r="R84" s="52"/>
+    </row>
+    <row r="85" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="49"/>
+      <c r="C85" s="40"/>
       <c r="D85" s="11">
         <v>0.5</v>
       </c>
@@ -3336,7 +3338,7 @@
         <v>15</v>
       </c>
       <c r="H85" s="25"/>
-      <c r="I85" s="29"/>
+      <c r="I85" s="40"/>
       <c r="J85" s="9">
         <v>1</v>
       </c>
@@ -3348,18 +3350,18 @@
       </c>
       <c r="M85" s="25"/>
       <c r="N85" s="25"/>
-      <c r="O85" s="29"/>
+      <c r="O85" s="40"/>
       <c r="P85" s="9">
         <v>2</v>
       </c>
-      <c r="Q85" s="40" t="s">
+      <c r="Q85" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="R85" s="42"/>
-    </row>
-    <row r="86" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="28"/>
-      <c r="C86" s="29"/>
+      <c r="R85" s="54"/>
+    </row>
+    <row r="86" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="49"/>
+      <c r="C86" s="40"/>
       <c r="D86" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -3373,71 +3375,71 @@
         <v>13</v>
       </c>
       <c r="H86" s="25"/>
-      <c r="I86" s="29"/>
+      <c r="I86" s="40"/>
       <c r="J86" s="9"/>
       <c r="K86" s="9"/>
       <c r="L86" s="9"/>
       <c r="M86" s="25"/>
       <c r="N86" s="25"/>
-      <c r="O86" s="29"/>
+      <c r="O86" s="40"/>
       <c r="P86" s="9">
         <v>1</v>
       </c>
-      <c r="Q86" s="33"/>
-      <c r="R86" s="34"/>
-    </row>
-    <row r="87" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="27" t="s">
+      <c r="Q86" s="41"/>
+      <c r="R86" s="42"/>
+    </row>
+    <row r="87" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C88" s="27"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
-      <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
-      <c r="J88" s="27"/>
-      <c r="K88" s="27"/>
-      <c r="L88" s="27"/>
-      <c r="M88" s="27"/>
-      <c r="N88" s="27"/>
-      <c r="O88" s="27"/>
-      <c r="P88" s="27"/>
-      <c r="Q88" s="27"/>
-      <c r="R88" s="27"/>
-    </row>
-    <row r="89" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="28" t="s">
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="28"/>
+      <c r="J88" s="28"/>
+      <c r="K88" s="28"/>
+      <c r="L88" s="28"/>
+      <c r="M88" s="28"/>
+      <c r="N88" s="28"/>
+      <c r="O88" s="28"/>
+      <c r="P88" s="28"/>
+      <c r="Q88" s="28"/>
+      <c r="R88" s="28"/>
+    </row>
+    <row r="89" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C89" s="29"/>
+      <c r="C89" s="40"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
-      <c r="F89" s="30" t="s">
+      <c r="F89" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G89" s="30"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="29"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="40"/>
       <c r="J89" s="9"/>
-      <c r="K89" s="30" t="s">
+      <c r="K89" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="30"/>
-      <c r="M89" s="30"/>
-      <c r="N89" s="30"/>
-      <c r="O89" s="29"/>
-      <c r="P89" s="30" t="s">
+      <c r="L89" s="50"/>
+      <c r="M89" s="50"/>
+      <c r="N89" s="50"/>
+      <c r="O89" s="40"/>
+      <c r="P89" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="30"/>
-      <c r="R89" s="30"/>
-    </row>
-    <row r="90" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="28"/>
-      <c r="C90" s="29"/>
+      <c r="Q89" s="50"/>
+      <c r="R89" s="50"/>
+    </row>
+    <row r="90" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="49"/>
+      <c r="C90" s="40"/>
       <c r="D90" s="9" t="s">
         <v>8</v>
       </c>
@@ -3453,7 +3455,7 @@
       <c r="H90" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I90" s="29"/>
+      <c r="I90" s="40"/>
       <c r="J90" s="9" t="s">
         <v>7</v>
       </c>
@@ -3469,18 +3471,18 @@
       <c r="N90" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O90" s="29"/>
+      <c r="O90" s="40"/>
       <c r="P90" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q90" s="30" t="s">
+      <c r="Q90" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R90" s="30"/>
-    </row>
-    <row r="91" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="28"/>
-      <c r="C91" s="29"/>
+      <c r="R90" s="50"/>
+    </row>
+    <row r="91" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="49"/>
+      <c r="C91" s="40"/>
       <c r="D91" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -3494,7 +3496,7 @@
         <v>46</v>
       </c>
       <c r="H91" s="25"/>
-      <c r="I91" s="29"/>
+      <c r="I91" s="40"/>
       <c r="J91" s="9">
         <v>1</v>
       </c>
@@ -3506,16 +3508,16 @@
       </c>
       <c r="M91" s="25"/>
       <c r="N91" s="24"/>
-      <c r="O91" s="29"/>
+      <c r="O91" s="40"/>
       <c r="P91" s="9">
         <v>3</v>
       </c>
-      <c r="Q91" s="31"/>
-      <c r="R91" s="32"/>
-    </row>
-    <row r="92" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="28"/>
-      <c r="C92" s="29"/>
+      <c r="Q91" s="51"/>
+      <c r="R91" s="52"/>
+    </row>
+    <row r="92" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="49"/>
+      <c r="C92" s="40"/>
       <c r="D92" s="11">
         <v>0.5</v>
       </c>
@@ -3529,7 +3531,7 @@
         <v>15</v>
       </c>
       <c r="H92" s="25"/>
-      <c r="I92" s="29"/>
+      <c r="I92" s="40"/>
       <c r="J92" s="9">
         <v>1</v>
       </c>
@@ -3541,18 +3543,18 @@
       </c>
       <c r="M92" s="25"/>
       <c r="N92" s="25"/>
-      <c r="O92" s="29"/>
+      <c r="O92" s="40"/>
       <c r="P92" s="9">
         <v>2</v>
       </c>
-      <c r="Q92" s="33" t="s">
+      <c r="Q92" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="R92" s="34"/>
-    </row>
-    <row r="93" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="28"/>
-      <c r="C93" s="29"/>
+      <c r="R92" s="42"/>
+    </row>
+    <row r="93" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="49"/>
+      <c r="C93" s="40"/>
       <c r="D93" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -3566,75 +3568,75 @@
         <v>13</v>
       </c>
       <c r="H93" s="25"/>
-      <c r="I93" s="29"/>
+      <c r="I93" s="40"/>
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
       <c r="L93" s="9"/>
       <c r="M93" s="25"/>
       <c r="N93" s="25"/>
-      <c r="O93" s="29"/>
+      <c r="O93" s="40"/>
       <c r="P93" s="9">
         <v>1</v>
       </c>
-      <c r="Q93" s="33"/>
-      <c r="R93" s="34"/>
-    </row>
-    <row r="94" spans="2:18" s="10" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q93" s="41"/>
+      <c r="R93" s="42"/>
+    </row>
+    <row r="94" spans="2:18" s="10" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="13"/>
     </row>
-    <row r="95" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="27" t="s">
+    <row r="95" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C95" s="27"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="27"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="27"/>
-      <c r="H95" s="27"/>
-      <c r="I95" s="27"/>
-      <c r="J95" s="27"/>
-      <c r="K95" s="27"/>
-      <c r="L95" s="27"/>
-      <c r="M95" s="27"/>
-      <c r="N95" s="27"/>
-      <c r="O95" s="27"/>
-      <c r="P95" s="27"/>
-      <c r="Q95" s="27"/>
-      <c r="R95" s="27"/>
-    </row>
-    <row r="96" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="28" t="s">
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
+      <c r="J95" s="28"/>
+      <c r="K95" s="28"/>
+      <c r="L95" s="28"/>
+      <c r="M95" s="28"/>
+      <c r="N95" s="28"/>
+      <c r="O95" s="28"/>
+      <c r="P95" s="28"/>
+      <c r="Q95" s="28"/>
+      <c r="R95" s="28"/>
+    </row>
+    <row r="96" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C96" s="29"/>
+      <c r="C96" s="40"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
-      <c r="F96" s="30" t="s">
+      <c r="F96" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="29"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="40"/>
       <c r="J96" s="9"/>
-      <c r="K96" s="30" t="s">
+      <c r="K96" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="30"/>
-      <c r="M96" s="30"/>
-      <c r="N96" s="30"/>
-      <c r="O96" s="29"/>
-      <c r="P96" s="30" t="s">
+      <c r="L96" s="50"/>
+      <c r="M96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="40"/>
+      <c r="P96" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="30"/>
-      <c r="R96" s="30"/>
-    </row>
-    <row r="97" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="28"/>
-      <c r="C97" s="29"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+    </row>
+    <row r="97" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="49"/>
+      <c r="C97" s="40"/>
       <c r="D97" s="9" t="s">
         <v>8</v>
       </c>
@@ -3650,7 +3652,7 @@
       <c r="H97" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I97" s="29"/>
+      <c r="I97" s="40"/>
       <c r="J97" s="9" t="s">
         <v>7</v>
       </c>
@@ -3666,18 +3668,18 @@
       <c r="N97" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O97" s="29"/>
+      <c r="O97" s="40"/>
       <c r="P97" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q97" s="30" t="s">
+      <c r="Q97" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R97" s="30"/>
-    </row>
-    <row r="98" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="28"/>
-      <c r="C98" s="29"/>
+      <c r="R97" s="50"/>
+    </row>
+    <row r="98" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="49"/>
+      <c r="C98" s="40"/>
       <c r="D98" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -3691,7 +3693,7 @@
         <v>13</v>
       </c>
       <c r="H98" s="9"/>
-      <c r="I98" s="29"/>
+      <c r="I98" s="40"/>
       <c r="J98" s="9">
         <v>2</v>
       </c>
@@ -3703,16 +3705,16 @@
       </c>
       <c r="M98" s="9"/>
       <c r="N98" s="24"/>
-      <c r="O98" s="29"/>
+      <c r="O98" s="40"/>
       <c r="P98" s="9">
         <v>3</v>
       </c>
-      <c r="Q98" s="31"/>
-      <c r="R98" s="32"/>
-    </row>
-    <row r="99" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="28"/>
-      <c r="C99" s="29"/>
+      <c r="Q98" s="51"/>
+      <c r="R98" s="52"/>
+    </row>
+    <row r="99" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="49"/>
+      <c r="C99" s="40"/>
       <c r="D99" s="11">
         <v>0.5</v>
       </c>
@@ -3726,7 +3728,7 @@
         <v>28</v>
       </c>
       <c r="H99" s="9"/>
-      <c r="I99" s="29"/>
+      <c r="I99" s="40"/>
       <c r="J99" s="9">
         <v>1</v>
       </c>
@@ -3738,18 +3740,18 @@
       </c>
       <c r="M99" s="9"/>
       <c r="N99" s="9"/>
-      <c r="O99" s="29"/>
+      <c r="O99" s="40"/>
       <c r="P99" s="9">
         <v>2</v>
       </c>
-      <c r="Q99" s="33" t="s">
+      <c r="Q99" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="R99" s="34"/>
-    </row>
-    <row r="100" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="28"/>
-      <c r="C100" s="29"/>
+      <c r="R99" s="42"/>
+    </row>
+    <row r="100" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="49"/>
+      <c r="C100" s="40"/>
       <c r="D100" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -3757,7 +3759,7 @@
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="25"/>
-      <c r="I100" s="29"/>
+      <c r="I100" s="40"/>
       <c r="J100" s="9">
         <v>1</v>
       </c>
@@ -3769,65 +3771,65 @@
       </c>
       <c r="M100" s="9"/>
       <c r="N100" s="9"/>
-      <c r="O100" s="29"/>
+      <c r="O100" s="40"/>
       <c r="P100" s="9">
         <v>1</v>
       </c>
-      <c r="Q100" s="33"/>
-      <c r="R100" s="34"/>
-    </row>
-    <row r="101" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="27" t="s">
+      <c r="Q100" s="41"/>
+      <c r="R100" s="42"/>
+    </row>
+    <row r="101" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="27"/>
-      <c r="I102" s="27"/>
-      <c r="J102" s="27"/>
-      <c r="K102" s="27"/>
-      <c r="L102" s="27"/>
-      <c r="M102" s="27"/>
-      <c r="N102" s="27"/>
-      <c r="O102" s="27"/>
-      <c r="P102" s="27"/>
-      <c r="Q102" s="27"/>
-      <c r="R102" s="27"/>
-    </row>
-    <row r="103" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="28" t="s">
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="28"/>
+      <c r="K102" s="28"/>
+      <c r="L102" s="28"/>
+      <c r="M102" s="28"/>
+      <c r="N102" s="28"/>
+      <c r="O102" s="28"/>
+      <c r="P102" s="28"/>
+      <c r="Q102" s="28"/>
+      <c r="R102" s="28"/>
+    </row>
+    <row r="103" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C103" s="29"/>
+      <c r="C103" s="40"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
-      <c r="F103" s="30" t="s">
+      <c r="F103" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="29"/>
+      <c r="G103" s="50"/>
+      <c r="H103" s="50"/>
+      <c r="I103" s="40"/>
       <c r="J103" s="9"/>
-      <c r="K103" s="30" t="s">
+      <c r="K103" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L103" s="30"/>
-      <c r="M103" s="30"/>
-      <c r="N103" s="30"/>
-      <c r="O103" s="29"/>
-      <c r="P103" s="30" t="s">
+      <c r="L103" s="50"/>
+      <c r="M103" s="50"/>
+      <c r="N103" s="50"/>
+      <c r="O103" s="40"/>
+      <c r="P103" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q103" s="30"/>
-      <c r="R103" s="30"/>
-    </row>
-    <row r="104" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="28"/>
-      <c r="C104" s="29"/>
+      <c r="Q103" s="50"/>
+      <c r="R103" s="50"/>
+    </row>
+    <row r="104" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="49"/>
+      <c r="C104" s="40"/>
       <c r="D104" s="9" t="s">
         <v>8</v>
       </c>
@@ -3843,7 +3845,7 @@
       <c r="H104" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I104" s="29"/>
+      <c r="I104" s="40"/>
       <c r="J104" s="9" t="s">
         <v>7</v>
       </c>
@@ -3859,18 +3861,18 @@
       <c r="N104" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O104" s="29"/>
+      <c r="O104" s="40"/>
       <c r="P104" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q104" s="30" t="s">
+      <c r="Q104" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="R104" s="30"/>
-    </row>
-    <row r="105" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="28"/>
-      <c r="C105" s="29"/>
+      <c r="R104" s="50"/>
+    </row>
+    <row r="105" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="49"/>
+      <c r="C105" s="40"/>
       <c r="D105" s="11">
         <v>0.44791666666666669</v>
       </c>
@@ -3884,7 +3886,7 @@
         <v>15</v>
       </c>
       <c r="H105" s="9"/>
-      <c r="I105" s="29"/>
+      <c r="I105" s="40"/>
       <c r="J105" s="9">
         <v>2</v>
       </c>
@@ -3896,16 +3898,16 @@
       </c>
       <c r="M105" s="9"/>
       <c r="N105" s="24"/>
-      <c r="O105" s="29"/>
+      <c r="O105" s="40"/>
       <c r="P105" s="9">
         <v>3</v>
       </c>
-      <c r="Q105" s="31"/>
-      <c r="R105" s="32"/>
-    </row>
-    <row r="106" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="28"/>
-      <c r="C106" s="29"/>
+      <c r="Q105" s="51"/>
+      <c r="R105" s="52"/>
+    </row>
+    <row r="106" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="49"/>
+      <c r="C106" s="40"/>
       <c r="D106" s="11">
         <v>0.5</v>
       </c>
@@ -3919,7 +3921,7 @@
         <v>46</v>
       </c>
       <c r="H106" s="9"/>
-      <c r="I106" s="29"/>
+      <c r="I106" s="40"/>
       <c r="J106" s="9">
         <v>1</v>
       </c>
@@ -3931,18 +3933,18 @@
       </c>
       <c r="M106" s="9"/>
       <c r="N106" s="9"/>
-      <c r="O106" s="29"/>
+      <c r="O106" s="40"/>
       <c r="P106" s="9">
         <v>2</v>
       </c>
-      <c r="Q106" s="33" t="s">
+      <c r="Q106" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="R106" s="34"/>
-    </row>
-    <row r="107" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="28"/>
-      <c r="C107" s="29"/>
+      <c r="R106" s="42"/>
+    </row>
+    <row r="107" spans="2:18" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="49"/>
+      <c r="C107" s="40"/>
       <c r="D107" s="11">
         <v>0.55208333333333337</v>
       </c>
@@ -3950,7 +3952,7 @@
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
-      <c r="I107" s="29"/>
+      <c r="I107" s="40"/>
       <c r="J107" s="9">
         <v>1</v>
       </c>
@@ -3962,72 +3964,72 @@
       </c>
       <c r="M107" s="25"/>
       <c r="N107" s="25"/>
-      <c r="O107" s="29"/>
+      <c r="O107" s="40"/>
       <c r="P107" s="9">
         <v>1</v>
       </c>
-      <c r="Q107" s="33"/>
-      <c r="R107" s="34"/>
-    </row>
-    <row r="108" spans="2:18" s="10" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q107" s="41"/>
+      <c r="R107" s="42"/>
+    </row>
+    <row r="108" spans="2:18" s="10" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="13"/>
     </row>
-    <row r="109" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="27" t="s">
+    <row r="109" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="27"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="27"/>
-      <c r="J109" s="27"/>
-      <c r="K109" s="27"/>
-      <c r="L109" s="27"/>
-      <c r="M109" s="27"/>
-      <c r="N109" s="27"/>
-      <c r="O109" s="27"/>
-      <c r="P109" s="27"/>
-      <c r="Q109" s="27"/>
-      <c r="R109" s="27"/>
-    </row>
-    <row r="110" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="28"/>
+      <c r="L109" s="28"/>
+      <c r="M109" s="28"/>
+      <c r="N109" s="28"/>
+      <c r="O109" s="28"/>
+      <c r="P109" s="28"/>
+      <c r="Q109" s="28"/>
+      <c r="R109" s="28"/>
+    </row>
+    <row r="110" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="43" t="s">
         <v>21</v>
       </c>
       <c r="C110" s="21"/>
       <c r="D110" s="14"/>
       <c r="E110" s="14"/>
-      <c r="F110" s="60"/>
-      <c r="G110" s="61"/>
-      <c r="H110" s="62"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="31"/>
+      <c r="H110" s="32"/>
       <c r="I110" s="16"/>
       <c r="J110" s="14"/>
-      <c r="K110" s="69" t="s">
+      <c r="K110" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="L110" s="70"/>
-      <c r="M110" s="70"/>
-      <c r="N110" s="71"/>
+      <c r="L110" s="47"/>
+      <c r="M110" s="47"/>
+      <c r="N110" s="48"/>
       <c r="O110" s="15"/>
-      <c r="P110" s="60"/>
-      <c r="Q110" s="61"/>
-      <c r="R110" s="62"/>
-    </row>
-    <row r="111" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P110" s="30"/>
+      <c r="Q110" s="31"/>
+      <c r="R110" s="32"/>
+    </row>
+    <row r="111" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="44"/>
       <c r="C111" s="22"/>
       <c r="D111" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E111" s="14"/>
-      <c r="F111" s="63"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="65"/>
+      <c r="F111" s="33"/>
+      <c r="G111" s="34"/>
+      <c r="H111" s="35"/>
       <c r="I111" s="18"/>
       <c r="J111" s="14" t="s">
         <v>7</v>
@@ -4045,20 +4047,20 @@
         <v>3</v>
       </c>
       <c r="O111" s="17"/>
-      <c r="P111" s="63"/>
-      <c r="Q111" s="64"/>
-      <c r="R111" s="65"/>
-    </row>
-    <row r="112" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P111" s="33"/>
+      <c r="Q111" s="34"/>
+      <c r="R111" s="35"/>
+    </row>
+    <row r="112" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="44"/>
       <c r="C112" s="22"/>
       <c r="D112" s="11">
         <v>0.5</v>
       </c>
       <c r="E112" s="14"/>
-      <c r="F112" s="63"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="65"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="35"/>
       <c r="I112" s="18"/>
       <c r="J112" s="14">
         <v>2</v>
@@ -4074,20 +4076,20 @@
       </c>
       <c r="N112" s="26"/>
       <c r="O112" s="17"/>
-      <c r="P112" s="63"/>
-      <c r="Q112" s="64"/>
-      <c r="R112" s="65"/>
-    </row>
-    <row r="113" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P112" s="33"/>
+      <c r="Q112" s="34"/>
+      <c r="R112" s="35"/>
+    </row>
+    <row r="113" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="45"/>
       <c r="C113" s="23"/>
       <c r="D113" s="11">
         <v>0.55208333333333337</v>
       </c>
       <c r="E113" s="14"/>
-      <c r="F113" s="66"/>
-      <c r="G113" s="67"/>
-      <c r="H113" s="68"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="37"/>
+      <c r="H113" s="38"/>
       <c r="I113" s="20"/>
       <c r="J113" s="14">
         <v>1</v>
@@ -4105,69 +4107,69 @@
         <v>22</v>
       </c>
       <c r="O113" s="19"/>
-      <c r="P113" s="66"/>
-      <c r="Q113" s="67"/>
-      <c r="R113" s="68"/>
-    </row>
-    <row r="114" spans="2:18" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P113" s="36"/>
+      <c r="Q113" s="37"/>
+      <c r="R113" s="38"/>
+    </row>
+    <row r="114" spans="2:18" s="8" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="27" t="s">
+    <row r="115" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="27"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="27"/>
-      <c r="J115" s="27"/>
-      <c r="K115" s="27"/>
-      <c r="L115" s="27"/>
-      <c r="M115" s="27"/>
-      <c r="N115" s="27"/>
-      <c r="O115" s="27"/>
-      <c r="P115" s="27"/>
-      <c r="Q115" s="27"/>
-      <c r="R115" s="27"/>
-    </row>
-    <row r="116" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="59" t="s">
+      <c r="C115" s="28"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="28"/>
+      <c r="H115" s="28"/>
+      <c r="I115" s="28"/>
+      <c r="J115" s="28"/>
+      <c r="K115" s="28"/>
+      <c r="L115" s="28"/>
+      <c r="M115" s="28"/>
+      <c r="N115" s="28"/>
+      <c r="O115" s="28"/>
+      <c r="P115" s="28"/>
+      <c r="Q115" s="28"/>
+      <c r="R115" s="28"/>
+    </row>
+    <row r="116" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C116" s="59"/>
+      <c r="C116" s="29"/>
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
-      <c r="F116" s="60"/>
-      <c r="G116" s="61"/>
-      <c r="H116" s="62"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="31"/>
+      <c r="H116" s="32"/>
       <c r="I116" s="16"/>
       <c r="J116" s="14"/>
-      <c r="K116" s="46" t="s">
+      <c r="K116" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L116" s="46"/>
-      <c r="M116" s="46"/>
-      <c r="N116" s="46"/>
-      <c r="O116" s="29"/>
-      <c r="P116" s="46"/>
-      <c r="Q116" s="46"/>
-      <c r="R116" s="46"/>
-    </row>
-    <row r="117" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="59"/>
-      <c r="C117" s="59"/>
+      <c r="L116" s="39"/>
+      <c r="M116" s="39"/>
+      <c r="N116" s="39"/>
+      <c r="O116" s="40"/>
+      <c r="P116" s="39"/>
+      <c r="Q116" s="39"/>
+      <c r="R116" s="39"/>
+    </row>
+    <row r="117" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E117" s="14"/>
-      <c r="F117" s="63"/>
-      <c r="G117" s="64"/>
-      <c r="H117" s="65"/>
+      <c r="F117" s="33"/>
+      <c r="G117" s="34"/>
+      <c r="H117" s="35"/>
       <c r="I117" s="18"/>
       <c r="J117" s="14" t="s">
         <v>7</v>
@@ -4184,23 +4186,23 @@
       <c r="N117" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="O117" s="29"/>
-      <c r="P117" s="46"/>
-      <c r="Q117" s="46"/>
-      <c r="R117" s="46"/>
-    </row>
-    <row r="118" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="59"/>
-      <c r="C118" s="59"/>
+      <c r="O117" s="40"/>
+      <c r="P117" s="39"/>
+      <c r="Q117" s="39"/>
+      <c r="R117" s="39"/>
+    </row>
+    <row r="118" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
       <c r="D118" s="11">
         <v>0.5</v>
       </c>
       <c r="E118" s="14">
         <v>2</v>
       </c>
-      <c r="F118" s="63"/>
-      <c r="G118" s="64"/>
-      <c r="H118" s="65"/>
+      <c r="F118" s="33"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="35"/>
       <c r="I118" s="18"/>
       <c r="J118" s="14">
         <v>2</v>
@@ -4213,23 +4215,23 @@
       </c>
       <c r="M118" s="14"/>
       <c r="N118" s="14"/>
-      <c r="O118" s="29"/>
-      <c r="P118" s="46"/>
-      <c r="Q118" s="46"/>
-      <c r="R118" s="46"/>
-    </row>
-    <row r="119" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="59"/>
-      <c r="C119" s="59"/>
+      <c r="O118" s="40"/>
+      <c r="P118" s="39"/>
+      <c r="Q118" s="39"/>
+      <c r="R118" s="39"/>
+    </row>
+    <row r="119" spans="2:18" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="11">
         <v>0.55208333333333337</v>
       </c>
       <c r="E119" s="14">
         <v>1</v>
       </c>
-      <c r="F119" s="66"/>
-      <c r="G119" s="67"/>
-      <c r="H119" s="68"/>
+      <c r="F119" s="36"/>
+      <c r="G119" s="37"/>
+      <c r="H119" s="38"/>
       <c r="I119" s="20"/>
       <c r="J119" s="14">
         <v>1</v>
@@ -4242,97 +4244,98 @@
       </c>
       <c r="M119" s="14"/>
       <c r="N119" s="14"/>
-      <c r="O119" s="29"/>
-      <c r="P119" s="46"/>
-      <c r="Q119" s="46"/>
-      <c r="R119" s="46"/>
+      <c r="O119" s="40"/>
+      <c r="P119" s="39"/>
+      <c r="Q119" s="39"/>
+      <c r="R119" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="193">
-    <mergeCell ref="B115:R115"/>
-    <mergeCell ref="B116:B119"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="F116:H119"/>
-    <mergeCell ref="K116:N116"/>
-    <mergeCell ref="O116:O119"/>
-    <mergeCell ref="P116:R119"/>
-    <mergeCell ref="Q106:R106"/>
-    <mergeCell ref="Q107:R107"/>
-    <mergeCell ref="B109:R109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="F110:H113"/>
-    <mergeCell ref="K110:N110"/>
-    <mergeCell ref="P110:R113"/>
-    <mergeCell ref="B102:R102"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:C107"/>
-    <mergeCell ref="F103:H103"/>
-    <mergeCell ref="I103:I107"/>
-    <mergeCell ref="K103:N103"/>
-    <mergeCell ref="O103:O107"/>
-    <mergeCell ref="P103:R103"/>
-    <mergeCell ref="Q104:R104"/>
-    <mergeCell ref="Q105:R105"/>
-    <mergeCell ref="P96:R96"/>
-    <mergeCell ref="Q97:R97"/>
-    <mergeCell ref="Q98:R98"/>
-    <mergeCell ref="Q99:R99"/>
-    <mergeCell ref="Q100:R100"/>
-    <mergeCell ref="B96:B100"/>
-    <mergeCell ref="C96:C100"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="I96:I100"/>
-    <mergeCell ref="K96:N96"/>
-    <mergeCell ref="O96:O100"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="Q91:R91"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="Q93:R93"/>
-    <mergeCell ref="B95:R95"/>
-    <mergeCell ref="Q86:R86"/>
-    <mergeCell ref="B88:R88"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="C89:C93"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="I89:I93"/>
-    <mergeCell ref="K89:N89"/>
-    <mergeCell ref="O89:O93"/>
-    <mergeCell ref="P89:R89"/>
-    <mergeCell ref="B81:R81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:I86"/>
-    <mergeCell ref="K82:N82"/>
-    <mergeCell ref="O82:O86"/>
-    <mergeCell ref="P82:R82"/>
-    <mergeCell ref="Q83:R83"/>
-    <mergeCell ref="Q84:R84"/>
-    <mergeCell ref="Q85:R85"/>
-    <mergeCell ref="O75:O79"/>
-    <mergeCell ref="P75:R75"/>
-    <mergeCell ref="Q76:R76"/>
-    <mergeCell ref="Q77:R77"/>
-    <mergeCell ref="Q78:R78"/>
-    <mergeCell ref="Q79:R79"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="Q71:R71"/>
-    <mergeCell ref="Q72:R72"/>
-    <mergeCell ref="B74:R74"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="I75:I79"/>
-    <mergeCell ref="K75:N75"/>
-    <mergeCell ref="B67:R67"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="I68:I72"/>
-    <mergeCell ref="K68:N68"/>
-    <mergeCell ref="O68:O72"/>
-    <mergeCell ref="P68:R68"/>
-    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:O7"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="B9:R9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:I14"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:O14"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="O17:O21"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="B16:R16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="B23:R23"/>
+    <mergeCell ref="B25:R25"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:I30"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="O26:O30"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="O33:O37"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="B32:R32"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:I37"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B39:R39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:I44"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="O40:O44"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="Q43:R43"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="B46:R46"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:I51"/>
+    <mergeCell ref="K47:N47"/>
+    <mergeCell ref="O47:O51"/>
+    <mergeCell ref="P47:R47"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="Q51:R51"/>
     <mergeCell ref="B53:R53"/>
     <mergeCell ref="B54:B58"/>
     <mergeCell ref="C54:C58"/>
@@ -4357,91 +4360,90 @@
     <mergeCell ref="K61:N61"/>
     <mergeCell ref="Q57:R57"/>
     <mergeCell ref="F56:H58"/>
-    <mergeCell ref="B46:R46"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I47:I51"/>
-    <mergeCell ref="K47:N47"/>
-    <mergeCell ref="O47:O51"/>
-    <mergeCell ref="P47:R47"/>
-    <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="Q51:R51"/>
-    <mergeCell ref="B39:R39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:I44"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="O40:O44"/>
-    <mergeCell ref="P40:R40"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="O33:O37"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="B32:R32"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:I37"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="B23:R23"/>
-    <mergeCell ref="B25:R25"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="O26:O30"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="B9:R9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:I14"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:O14"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="O17:O21"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="B16:R16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:O7"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="B67:R67"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="I68:I72"/>
+    <mergeCell ref="K68:N68"/>
+    <mergeCell ref="O68:O72"/>
+    <mergeCell ref="P68:R68"/>
+    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="O75:O79"/>
+    <mergeCell ref="P75:R75"/>
+    <mergeCell ref="Q76:R76"/>
+    <mergeCell ref="Q77:R77"/>
+    <mergeCell ref="Q78:R78"/>
+    <mergeCell ref="Q79:R79"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="Q71:R71"/>
+    <mergeCell ref="Q72:R72"/>
+    <mergeCell ref="B74:R74"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="I75:I79"/>
+    <mergeCell ref="K75:N75"/>
+    <mergeCell ref="B81:R81"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:I86"/>
+    <mergeCell ref="K82:N82"/>
+    <mergeCell ref="O82:O86"/>
+    <mergeCell ref="P82:R82"/>
+    <mergeCell ref="Q83:R83"/>
+    <mergeCell ref="Q84:R84"/>
+    <mergeCell ref="Q85:R85"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="Q91:R91"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="Q93:R93"/>
+    <mergeCell ref="B95:R95"/>
+    <mergeCell ref="Q86:R86"/>
+    <mergeCell ref="B88:R88"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="C89:C93"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="I89:I93"/>
+    <mergeCell ref="K89:N89"/>
+    <mergeCell ref="O89:O93"/>
+    <mergeCell ref="P89:R89"/>
+    <mergeCell ref="P96:R96"/>
+    <mergeCell ref="Q97:R97"/>
+    <mergeCell ref="Q98:R98"/>
+    <mergeCell ref="Q99:R99"/>
+    <mergeCell ref="Q100:R100"/>
+    <mergeCell ref="B96:B100"/>
+    <mergeCell ref="C96:C100"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="I96:I100"/>
+    <mergeCell ref="K96:N96"/>
+    <mergeCell ref="O96:O100"/>
+    <mergeCell ref="B102:R102"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="F103:H103"/>
+    <mergeCell ref="I103:I107"/>
+    <mergeCell ref="K103:N103"/>
+    <mergeCell ref="O103:O107"/>
+    <mergeCell ref="P103:R103"/>
+    <mergeCell ref="Q104:R104"/>
+    <mergeCell ref="Q105:R105"/>
+    <mergeCell ref="B115:R115"/>
+    <mergeCell ref="B116:B119"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="F116:H119"/>
+    <mergeCell ref="K116:N116"/>
+    <mergeCell ref="O116:O119"/>
+    <mergeCell ref="P116:R119"/>
+    <mergeCell ref="Q106:R106"/>
+    <mergeCell ref="Q107:R107"/>
+    <mergeCell ref="B109:R109"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="F110:H113"/>
+    <mergeCell ref="K110:N110"/>
+    <mergeCell ref="P110:R113"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4458,94 +4460,94 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4279675B-9D1E-4F40-AB5C-19D754BF5355}">
   <dimension ref="A1:AD143"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="4.140625" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
-    <col min="13" max="13" width="3.7109375" customWidth="1"/>
-    <col min="14" max="16" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="3.6640625" customWidth="1"/>
+    <col min="14" max="16" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="75"/>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="75"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="73"/>
-      <c r="B5" s="73"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="73"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
-      <c r="B6" s="73"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
       <c r="V6" s="5"/>
       <c r="X6" s="1"/>
       <c r="AA6" s="5"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="75"/>
+      <c r="B7" s="75"/>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
       <c r="H7" s="5"/>
@@ -4555,9 +4557,9 @@
       <c r="W7" s="1"/>
       <c r="AA7" s="5"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73"/>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="75"/>
+      <c r="B8" s="75"/>
       <c r="C8" s="4"/>
       <c r="D8" s="5"/>
       <c r="H8" s="5"/>
@@ -4567,56 +4569,56 @@
       <c r="V8" s="5"/>
       <c r="AA8" s="5"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73"/>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
       <c r="C9" s="4"/>
       <c r="D9" s="5"/>
       <c r="F9" s="2"/>
       <c r="H9" s="5"/>
       <c r="M9" s="5"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" s="75"/>
+      <c r="B13" s="75"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="73"/>
-      <c r="B14" s="73"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
-      <c r="B15" s="73"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" s="75"/>
+      <c r="B15" s="75"/>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
       <c r="F15" s="2"/>
@@ -4624,212 +4626,212 @@
       <c r="I15" s="1"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73"/>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" s="75"/>
+      <c r="B16" s="75"/>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
       <c r="H16" s="5"/>
       <c r="J16" s="1"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
-      <c r="B17" s="73"/>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="75"/>
+      <c r="B17" s="75"/>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
       <c r="H17" s="5"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="72"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
-      <c r="B22" s="73"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="74"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="74"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="74"/>
+      <c r="P21" s="74"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="75"/>
+      <c r="B22" s="75"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="73"/>
-      <c r="B23" s="73"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="73"/>
-      <c r="B24" s="73"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="75"/>
+      <c r="B23" s="75"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="75"/>
+      <c r="B24" s="75"/>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
       <c r="F24" s="2"/>
       <c r="H24" s="5"/>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73"/>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="75"/>
+      <c r="B25" s="75"/>
       <c r="C25" s="4"/>
       <c r="D25" s="5"/>
       <c r="F25" s="1"/>
       <c r="H25" s="5"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="1"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="72"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" s="75"/>
+      <c r="B30" s="75"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
-      <c r="B32" s="73"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" s="75"/>
+      <c r="B31" s="75"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="75"/>
+      <c r="B32" s="75"/>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
       <c r="H32" s="5"/>
       <c r="J32" s="1"/>
       <c r="M32" s="5"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
-      <c r="B33" s="73"/>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" s="75"/>
+      <c r="B33" s="75"/>
       <c r="C33" s="4"/>
       <c r="D33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="1"/>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
-      <c r="B34" s="73"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="75"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="4"/>
       <c r="D34" s="5"/>
       <c r="E34" s="2"/>
       <c r="H34" s="5"/>
       <c r="M34" s="5"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="72"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="72"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="72"/>
-      <c r="P37" s="72"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="73"/>
-      <c r="B38" s="73"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" s="74"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="74"/>
+      <c r="L37" s="74"/>
+      <c r="M37" s="74"/>
+      <c r="N37" s="74"/>
+      <c r="O37" s="74"/>
+      <c r="P37" s="74"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" s="75"/>
+      <c r="B38" s="75"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="72"/>
-      <c r="P38" s="72"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="73"/>
-      <c r="B39" s="73"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="73"/>
-      <c r="B40" s="73"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="74"/>
+      <c r="L38" s="74"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="74"/>
+      <c r="P38" s="74"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" s="75"/>
+      <c r="B39" s="75"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="75"/>
+      <c r="B40" s="75"/>
       <c r="C40" s="4"/>
       <c r="D40" s="5"/>
       <c r="E40" s="2"/>
@@ -4838,17 +4840,17 @@
       <c r="N40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="73"/>
-      <c r="B41" s="73"/>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="75"/>
+      <c r="B41" s="75"/>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
       <c r="H41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
-      <c r="B42" s="73"/>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" s="75"/>
+      <c r="B42" s="75"/>
       <c r="C42" s="4"/>
       <c r="D42" s="5"/>
       <c r="H42" s="5"/>
@@ -4856,65 +4858,65 @@
       <c r="N42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="72"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-      <c r="P44" s="72"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="72"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72"/>
-      <c r="K46" s="72"/>
-      <c r="L46" s="72"/>
-      <c r="M46" s="72"/>
-      <c r="N46" s="72"/>
-      <c r="O46" s="72"/>
-      <c r="P46" s="72"/>
-    </row>
-    <row r="47" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="73"/>
-      <c r="B47" s="73"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="72"/>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="74"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="74"/>
+      <c r="P44" s="74"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" s="74"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="74"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="74"/>
+      <c r="P46" s="74"/>
+    </row>
+    <row r="47" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="75"/>
+      <c r="B47" s="75"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72"/>
-      <c r="K47" s="72"/>
-      <c r="L47" s="72"/>
-      <c r="M47" s="72"/>
-      <c r="N47" s="72"/>
-      <c r="O47" s="72"/>
-      <c r="P47" s="72"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="73"/>
-      <c r="B48" s="73"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="73"/>
-      <c r="B49" s="73"/>
+      <c r="I47" s="74"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="74"/>
+      <c r="N47" s="74"/>
+      <c r="O47" s="74"/>
+      <c r="P47" s="74"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="75"/>
+      <c r="B48" s="75"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="75"/>
+      <c r="B49" s="75"/>
       <c r="C49" s="4"/>
       <c r="D49" s="5"/>
       <c r="F49" s="2"/>
@@ -4922,65 +4924,65 @@
       <c r="J49" s="1"/>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="73"/>
-      <c r="B50" s="73"/>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" s="75"/>
+      <c r="B50" s="75"/>
       <c r="C50" s="4"/>
       <c r="D50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="1"/>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="73"/>
-      <c r="B51" s="73"/>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" s="75"/>
+      <c r="B51" s="75"/>
       <c r="C51" s="4"/>
       <c r="D51" s="5"/>
       <c r="G51" s="3"/>
       <c r="H51" s="5"/>
       <c r="M51" s="5"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="72"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="72"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="72"/>
-      <c r="M54" s="72"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="72"/>
-      <c r="P54" s="72"/>
-    </row>
-    <row r="55" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="73"/>
-      <c r="B55" s="73"/>
-      <c r="E55" s="72"/>
-      <c r="F55" s="72"/>
-      <c r="G55" s="72"/>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" s="74"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="74"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="74"/>
+      <c r="P54" s="74"/>
+    </row>
+    <row r="55" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="75"/>
+      <c r="B55" s="75"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
       <c r="H55" s="5"/>
-      <c r="I55" s="72"/>
-      <c r="J55" s="72"/>
-      <c r="K55" s="72"/>
-      <c r="L55" s="72"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="72"/>
-      <c r="O55" s="72"/>
-      <c r="P55" s="72"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="73"/>
-      <c r="B56" s="73"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="73"/>
-      <c r="B57" s="73"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="74"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="74"/>
+      <c r="P55" s="74"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="75"/>
+      <c r="B56" s="75"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="75"/>
+      <c r="B57" s="75"/>
       <c r="C57" s="4"/>
       <c r="D57" s="5"/>
       <c r="E57" s="2"/>
@@ -4989,83 +4991,83 @@
       <c r="J57" s="1"/>
       <c r="M57" s="5"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="73"/>
-      <c r="B58" s="73"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="75"/>
+      <c r="B58" s="75"/>
       <c r="C58" s="4"/>
       <c r="D58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="1"/>
       <c r="M58" s="5"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="73"/>
-      <c r="B59" s="73"/>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="75"/>
+      <c r="B59" s="75"/>
       <c r="C59" s="4"/>
       <c r="D59" s="5"/>
       <c r="G59" s="3"/>
       <c r="H59" s="5"/>
       <c r="M59" s="5"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
-      <c r="J62" s="72"/>
-      <c r="K62" s="72"/>
-      <c r="L62" s="72"/>
-      <c r="M62" s="72"/>
-      <c r="N62" s="72"/>
-      <c r="O62" s="72"/>
-      <c r="P62" s="72"/>
-    </row>
-    <row r="63" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="73"/>
-      <c r="B63" s="73"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="72"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="74"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="74"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="74"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="74"/>
+      <c r="M62" s="74"/>
+      <c r="N62" s="74"/>
+      <c r="O62" s="74"/>
+      <c r="P62" s="74"/>
+    </row>
+    <row r="63" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="75"/>
+      <c r="B63" s="75"/>
+      <c r="E63" s="74"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="74"/>
       <c r="H63" s="5"/>
-      <c r="I63" s="72"/>
-      <c r="J63" s="72"/>
-      <c r="K63" s="72"/>
-      <c r="L63" s="72"/>
-      <c r="M63" s="72"/>
-      <c r="N63" s="72"/>
-      <c r="O63" s="72"/>
-      <c r="P63" s="72"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="73"/>
-      <c r="B64" s="73"/>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A65" s="73"/>
-      <c r="B65" s="73"/>
+      <c r="I63" s="74"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="74"/>
+      <c r="L63" s="74"/>
+      <c r="M63" s="74"/>
+      <c r="N63" s="74"/>
+      <c r="O63" s="74"/>
+      <c r="P63" s="74"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="75"/>
+      <c r="B64" s="75"/>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A65" s="75"/>
+      <c r="B65" s="75"/>
       <c r="C65" s="4"/>
       <c r="D65" s="5"/>
       <c r="G65" s="3"/>
       <c r="H65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A66" s="73"/>
-      <c r="B66" s="73"/>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A66" s="75"/>
+      <c r="B66" s="75"/>
       <c r="C66" s="4"/>
       <c r="D66" s="5"/>
       <c r="E66" s="1"/>
       <c r="H66" s="5"/>
       <c r="M66" s="5"/>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A67" s="73"/>
-      <c r="B67" s="73"/>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A67" s="75"/>
+      <c r="B67" s="75"/>
       <c r="C67" s="4"/>
       <c r="D67" s="5"/>
       <c r="F67" s="2"/>
@@ -5074,47 +5076,47 @@
       <c r="J67" s="1"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A70" s="72"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="72"/>
-      <c r="E70" s="72"/>
-      <c r="F70" s="72"/>
-      <c r="G70" s="72"/>
-      <c r="H70" s="72"/>
-      <c r="I70" s="72"/>
-      <c r="J70" s="72"/>
-      <c r="K70" s="72"/>
-      <c r="L70" s="72"/>
-      <c r="M70" s="72"/>
-      <c r="N70" s="72"/>
-      <c r="O70" s="72"/>
-      <c r="P70" s="72"/>
-    </row>
-    <row r="71" spans="1:27" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="73"/>
-      <c r="B71" s="73"/>
-      <c r="E71" s="72"/>
-      <c r="F71" s="72"/>
-      <c r="G71" s="72"/>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A70" s="74"/>
+      <c r="B70" s="74"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="74"/>
+      <c r="M70" s="74"/>
+      <c r="N70" s="74"/>
+      <c r="O70" s="74"/>
+      <c r="P70" s="74"/>
+    </row>
+    <row r="71" spans="1:27" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="75"/>
+      <c r="B71" s="75"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
       <c r="H71" s="5"/>
-      <c r="I71" s="72"/>
-      <c r="J71" s="72"/>
-      <c r="K71" s="72"/>
-      <c r="L71" s="72"/>
-      <c r="M71" s="72"/>
-      <c r="N71" s="72"/>
-      <c r="O71" s="72"/>
-      <c r="P71" s="72"/>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A72" s="73"/>
-      <c r="B72" s="73"/>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A73" s="73"/>
-      <c r="B73" s="73"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="74"/>
+      <c r="L71" s="74"/>
+      <c r="M71" s="74"/>
+      <c r="N71" s="74"/>
+      <c r="O71" s="74"/>
+      <c r="P71" s="74"/>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A72" s="75"/>
+      <c r="B72" s="75"/>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A73" s="75"/>
+      <c r="B73" s="75"/>
       <c r="C73" s="4"/>
       <c r="D73" s="5"/>
       <c r="G73" s="3"/>
@@ -5127,9 +5129,9 @@
       <c r="W73" s="1"/>
       <c r="AA73" s="5"/>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A74" s="73"/>
-      <c r="B74" s="73"/>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A74" s="75"/>
+      <c r="B74" s="75"/>
       <c r="C74" s="4"/>
       <c r="D74" s="5"/>
       <c r="H74" s="5"/>
@@ -5140,9 +5142,9 @@
       <c r="X74" s="1"/>
       <c r="AA74" s="5"/>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A75" s="73"/>
-      <c r="B75" s="73"/>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A75" s="75"/>
+      <c r="B75" s="75"/>
       <c r="C75" s="4"/>
       <c r="D75" s="5"/>
       <c r="G75" s="3"/>
@@ -5154,47 +5156,47 @@
       <c r="V75" s="5"/>
       <c r="AA75" s="5"/>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="72"/>
-      <c r="D78" s="72"/>
-      <c r="E78" s="72"/>
-      <c r="F78" s="72"/>
-      <c r="G78" s="72"/>
-      <c r="H78" s="72"/>
-      <c r="I78" s="72"/>
-      <c r="J78" s="72"/>
-      <c r="K78" s="72"/>
-      <c r="L78" s="72"/>
-      <c r="M78" s="72"/>
-      <c r="N78" s="72"/>
-      <c r="O78" s="72"/>
-      <c r="P78" s="72"/>
-    </row>
-    <row r="79" spans="1:27" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="73"/>
-      <c r="B79" s="73"/>
-      <c r="E79" s="72"/>
-      <c r="F79" s="72"/>
-      <c r="G79" s="72"/>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A78" s="74"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="74"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="74"/>
+      <c r="F78" s="74"/>
+      <c r="G78" s="74"/>
+      <c r="H78" s="74"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="74"/>
+      <c r="K78" s="74"/>
+      <c r="L78" s="74"/>
+      <c r="M78" s="74"/>
+      <c r="N78" s="74"/>
+      <c r="O78" s="74"/>
+      <c r="P78" s="74"/>
+    </row>
+    <row r="79" spans="1:27" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="75"/>
+      <c r="B79" s="75"/>
+      <c r="E79" s="74"/>
+      <c r="F79" s="74"/>
+      <c r="G79" s="74"/>
       <c r="H79" s="5"/>
-      <c r="I79" s="72"/>
-      <c r="J79" s="72"/>
-      <c r="K79" s="72"/>
-      <c r="L79" s="72"/>
-      <c r="M79" s="72"/>
-      <c r="N79" s="72"/>
-      <c r="O79" s="72"/>
-      <c r="P79" s="72"/>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A80" s="73"/>
-      <c r="B80" s="73"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="73"/>
-      <c r="B81" s="73"/>
+      <c r="I79" s="74"/>
+      <c r="J79" s="74"/>
+      <c r="K79" s="74"/>
+      <c r="L79" s="74"/>
+      <c r="M79" s="74"/>
+      <c r="N79" s="74"/>
+      <c r="O79" s="74"/>
+      <c r="P79" s="74"/>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A80" s="75"/>
+      <c r="B80" s="75"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" s="75"/>
+      <c r="B81" s="75"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5"/>
       <c r="F81" s="2"/>
@@ -5204,17 +5206,17 @@
       <c r="N81" s="1"/>
       <c r="P81" s="1"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="73"/>
-      <c r="B82" s="73"/>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" s="75"/>
+      <c r="B82" s="75"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5"/>
       <c r="H82" s="5"/>
       <c r="M82" s="5"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="73"/>
-      <c r="B83" s="73"/>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" s="75"/>
+      <c r="B83" s="75"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5"/>
       <c r="G83" s="3"/>
@@ -5223,47 +5225,47 @@
       <c r="N83" s="1"/>
       <c r="P83" s="1"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="72"/>
-      <c r="C86" s="72"/>
-      <c r="D86" s="72"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
-      <c r="L86" s="72"/>
-      <c r="M86" s="72"/>
-      <c r="N86" s="72"/>
-      <c r="O86" s="72"/>
-      <c r="P86" s="72"/>
-    </row>
-    <row r="87" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="73"/>
-      <c r="B87" s="73"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A86" s="74"/>
+      <c r="B86" s="74"/>
+      <c r="C86" s="74"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="74"/>
+      <c r="F86" s="74"/>
+      <c r="G86" s="74"/>
+      <c r="H86" s="74"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="74"/>
+      <c r="K86" s="74"/>
+      <c r="L86" s="74"/>
+      <c r="M86" s="74"/>
+      <c r="N86" s="74"/>
+      <c r="O86" s="74"/>
+      <c r="P86" s="74"/>
+    </row>
+    <row r="87" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="75"/>
+      <c r="B87" s="75"/>
+      <c r="E87" s="74"/>
+      <c r="F87" s="74"/>
+      <c r="G87" s="74"/>
       <c r="H87" s="5"/>
-      <c r="I87" s="72"/>
-      <c r="J87" s="72"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="72"/>
-      <c r="M87" s="72"/>
-      <c r="N87" s="72"/>
-      <c r="O87" s="72"/>
-      <c r="P87" s="72"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="73"/>
-      <c r="B88" s="73"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="73"/>
-      <c r="B89" s="73"/>
+      <c r="I87" s="74"/>
+      <c r="J87" s="74"/>
+      <c r="K87" s="74"/>
+      <c r="L87" s="74"/>
+      <c r="M87" s="74"/>
+      <c r="N87" s="74"/>
+      <c r="O87" s="74"/>
+      <c r="P87" s="74"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A88" s="75"/>
+      <c r="B88" s="75"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A89" s="75"/>
+      <c r="B89" s="75"/>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
       <c r="G89" s="3"/>
@@ -5271,18 +5273,18 @@
       <c r="I89" s="1"/>
       <c r="M89" s="5"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="73"/>
-      <c r="B90" s="73"/>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A90" s="75"/>
+      <c r="B90" s="75"/>
       <c r="C90" s="4"/>
       <c r="D90" s="5"/>
       <c r="H90" s="5"/>
       <c r="J90" s="1"/>
       <c r="M90" s="5"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="73"/>
-      <c r="B91" s="73"/>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" s="75"/>
+      <c r="B91" s="75"/>
       <c r="C91" s="4"/>
       <c r="D91" s="5"/>
       <c r="E91" s="2"/>
@@ -5290,47 +5292,47 @@
       <c r="H91" s="5"/>
       <c r="M91" s="5"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="72"/>
-      <c r="C94" s="72"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
-      <c r="H94" s="72"/>
-      <c r="I94" s="72"/>
-      <c r="J94" s="72"/>
-      <c r="K94" s="72"/>
-      <c r="L94" s="72"/>
-      <c r="M94" s="72"/>
-      <c r="N94" s="72"/>
-      <c r="O94" s="72"/>
-      <c r="P94" s="72"/>
-    </row>
-    <row r="95" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="73"/>
-      <c r="B95" s="73"/>
-      <c r="E95" s="72"/>
-      <c r="F95" s="72"/>
-      <c r="G95" s="72"/>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" s="74"/>
+      <c r="B94" s="74"/>
+      <c r="C94" s="74"/>
+      <c r="D94" s="74"/>
+      <c r="E94" s="74"/>
+      <c r="F94" s="74"/>
+      <c r="G94" s="74"/>
+      <c r="H94" s="74"/>
+      <c r="I94" s="74"/>
+      <c r="J94" s="74"/>
+      <c r="K94" s="74"/>
+      <c r="L94" s="74"/>
+      <c r="M94" s="74"/>
+      <c r="N94" s="74"/>
+      <c r="O94" s="74"/>
+      <c r="P94" s="74"/>
+    </row>
+    <row r="95" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="75"/>
+      <c r="B95" s="75"/>
+      <c r="E95" s="74"/>
+      <c r="F95" s="74"/>
+      <c r="G95" s="74"/>
       <c r="H95" s="5"/>
-      <c r="I95" s="72"/>
-      <c r="J95" s="72"/>
-      <c r="K95" s="72"/>
-      <c r="L95" s="72"/>
-      <c r="M95" s="72"/>
-      <c r="N95" s="72"/>
-      <c r="O95" s="72"/>
-      <c r="P95" s="72"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="73"/>
-      <c r="B96" s="73"/>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="73"/>
-      <c r="B97" s="73"/>
+      <c r="I95" s="74"/>
+      <c r="J95" s="74"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="74"/>
+      <c r="M95" s="74"/>
+      <c r="N95" s="74"/>
+      <c r="O95" s="74"/>
+      <c r="P95" s="74"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A96" s="75"/>
+      <c r="B96" s="75"/>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A97" s="75"/>
+      <c r="B97" s="75"/>
       <c r="C97" s="4"/>
       <c r="D97" s="5"/>
       <c r="G97" s="3"/>
@@ -5338,18 +5340,18 @@
       <c r="I97" s="1"/>
       <c r="M97" s="5"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="73"/>
-      <c r="B98" s="73"/>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A98" s="75"/>
+      <c r="B98" s="75"/>
       <c r="C98" s="4"/>
       <c r="D98" s="5"/>
       <c r="H98" s="5"/>
       <c r="J98" s="1"/>
       <c r="M98" s="5"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="73"/>
-      <c r="B99" s="73"/>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" s="75"/>
+      <c r="B99" s="75"/>
       <c r="C99" s="4"/>
       <c r="D99" s="5"/>
       <c r="F99" s="2"/>
@@ -5357,101 +5359,101 @@
       <c r="H99" s="5"/>
       <c r="M99" s="5"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="72"/>
-      <c r="B101" s="72"/>
-      <c r="C101" s="72"/>
-      <c r="D101" s="72"/>
-      <c r="E101" s="72"/>
-      <c r="F101" s="72"/>
-      <c r="G101" s="72"/>
-      <c r="H101" s="72"/>
-      <c r="I101" s="72"/>
-      <c r="J101" s="72"/>
-      <c r="K101" s="72"/>
-      <c r="L101" s="72"/>
-      <c r="M101" s="72"/>
-      <c r="N101" s="72"/>
-      <c r="O101" s="72"/>
-      <c r="P101" s="72"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="72"/>
-      <c r="B103" s="72"/>
-      <c r="C103" s="72"/>
-      <c r="D103" s="72"/>
-      <c r="E103" s="72"/>
-      <c r="F103" s="72"/>
-      <c r="G103" s="72"/>
-      <c r="H103" s="72"/>
-      <c r="I103" s="72"/>
-      <c r="J103" s="72"/>
-      <c r="K103" s="72"/>
-      <c r="L103" s="72"/>
-      <c r="M103" s="72"/>
-      <c r="N103" s="72"/>
-      <c r="O103" s="72"/>
-      <c r="P103" s="72"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="72"/>
-      <c r="B105" s="72"/>
-      <c r="C105" s="72"/>
-      <c r="D105" s="72"/>
-      <c r="E105" s="72"/>
-      <c r="F105" s="72"/>
-      <c r="G105" s="72"/>
-      <c r="H105" s="72"/>
-      <c r="I105" s="72"/>
-      <c r="J105" s="72"/>
-      <c r="K105" s="72"/>
-      <c r="L105" s="72"/>
-      <c r="M105" s="72"/>
-      <c r="N105" s="72"/>
-      <c r="O105" s="72"/>
-      <c r="P105" s="72"/>
-    </row>
-    <row r="106" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="73"/>
-      <c r="B106" s="73"/>
-      <c r="E106" s="72"/>
-      <c r="F106" s="72"/>
-      <c r="G106" s="72"/>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" s="74"/>
+      <c r="B101" s="74"/>
+      <c r="C101" s="74"/>
+      <c r="D101" s="74"/>
+      <c r="E101" s="74"/>
+      <c r="F101" s="74"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="74"/>
+      <c r="I101" s="74"/>
+      <c r="J101" s="74"/>
+      <c r="K101" s="74"/>
+      <c r="L101" s="74"/>
+      <c r="M101" s="74"/>
+      <c r="N101" s="74"/>
+      <c r="O101" s="74"/>
+      <c r="P101" s="74"/>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A103" s="74"/>
+      <c r="B103" s="74"/>
+      <c r="C103" s="74"/>
+      <c r="D103" s="74"/>
+      <c r="E103" s="74"/>
+      <c r="F103" s="74"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="74"/>
+      <c r="I103" s="74"/>
+      <c r="J103" s="74"/>
+      <c r="K103" s="74"/>
+      <c r="L103" s="74"/>
+      <c r="M103" s="74"/>
+      <c r="N103" s="74"/>
+      <c r="O103" s="74"/>
+      <c r="P103" s="74"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A105" s="74"/>
+      <c r="B105" s="74"/>
+      <c r="C105" s="74"/>
+      <c r="D105" s="74"/>
+      <c r="E105" s="74"/>
+      <c r="F105" s="74"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="74"/>
+      <c r="I105" s="74"/>
+      <c r="J105" s="74"/>
+      <c r="K105" s="74"/>
+      <c r="L105" s="74"/>
+      <c r="M105" s="74"/>
+      <c r="N105" s="74"/>
+      <c r="O105" s="74"/>
+      <c r="P105" s="74"/>
+    </row>
+    <row r="106" spans="1:16" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="75"/>
+      <c r="B106" s="75"/>
+      <c r="E106" s="74"/>
+      <c r="F106" s="74"/>
+      <c r="G106" s="74"/>
       <c r="H106" s="5"/>
-      <c r="I106" s="72"/>
-      <c r="J106" s="72"/>
-      <c r="K106" s="72"/>
-      <c r="L106" s="72"/>
-      <c r="M106" s="72"/>
-      <c r="N106" s="72"/>
-      <c r="O106" s="72"/>
-      <c r="P106" s="72"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="73"/>
-      <c r="B107" s="73"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="73"/>
-      <c r="B108" s="73"/>
+      <c r="I106" s="74"/>
+      <c r="J106" s="74"/>
+      <c r="K106" s="74"/>
+      <c r="L106" s="74"/>
+      <c r="M106" s="74"/>
+      <c r="N106" s="74"/>
+      <c r="O106" s="74"/>
+      <c r="P106" s="74"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A107" s="75"/>
+      <c r="B107" s="75"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A108" s="75"/>
+      <c r="B108" s="75"/>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
       <c r="G108" s="3"/>
       <c r="H108" s="5"/>
       <c r="M108" s="5"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="73"/>
-      <c r="B109" s="73"/>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A109" s="75"/>
+      <c r="B109" s="75"/>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
       <c r="F109" s="1"/>
       <c r="H109" s="5"/>
       <c r="M109" s="5"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="73"/>
-      <c r="B110" s="73"/>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A110" s="75"/>
+      <c r="B110" s="75"/>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
       <c r="F110" s="2"/>
@@ -5460,47 +5462,47 @@
       <c r="I110" s="1"/>
       <c r="M110" s="5"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A113" s="72"/>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
-      <c r="G113" s="72"/>
-      <c r="H113" s="72"/>
-      <c r="I113" s="72"/>
-      <c r="J113" s="72"/>
-      <c r="K113" s="72"/>
-      <c r="L113" s="72"/>
-      <c r="M113" s="72"/>
-      <c r="N113" s="72"/>
-      <c r="O113" s="72"/>
-      <c r="P113" s="72"/>
-    </row>
-    <row r="114" spans="1:30" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="73"/>
-      <c r="B114" s="73"/>
-      <c r="E114" s="72"/>
-      <c r="F114" s="72"/>
-      <c r="G114" s="72"/>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A113" s="74"/>
+      <c r="B113" s="74"/>
+      <c r="C113" s="74"/>
+      <c r="D113" s="74"/>
+      <c r="E113" s="74"/>
+      <c r="F113" s="74"/>
+      <c r="G113" s="74"/>
+      <c r="H113" s="74"/>
+      <c r="I113" s="74"/>
+      <c r="J113" s="74"/>
+      <c r="K113" s="74"/>
+      <c r="L113" s="74"/>
+      <c r="M113" s="74"/>
+      <c r="N113" s="74"/>
+      <c r="O113" s="74"/>
+      <c r="P113" s="74"/>
+    </row>
+    <row r="114" spans="1:30" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="75"/>
+      <c r="B114" s="75"/>
+      <c r="E114" s="74"/>
+      <c r="F114" s="74"/>
+      <c r="G114" s="74"/>
       <c r="H114" s="5"/>
-      <c r="I114" s="72"/>
-      <c r="J114" s="72"/>
-      <c r="K114" s="72"/>
-      <c r="L114" s="72"/>
-      <c r="M114" s="72"/>
-      <c r="N114" s="72"/>
-      <c r="O114" s="72"/>
-      <c r="P114" s="72"/>
-    </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A115" s="73"/>
-      <c r="B115" s="73"/>
-    </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A116" s="73"/>
-      <c r="B116" s="73"/>
+      <c r="I114" s="74"/>
+      <c r="J114" s="74"/>
+      <c r="K114" s="74"/>
+      <c r="L114" s="74"/>
+      <c r="M114" s="74"/>
+      <c r="N114" s="74"/>
+      <c r="O114" s="74"/>
+      <c r="P114" s="74"/>
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A115" s="75"/>
+      <c r="B115" s="75"/>
+    </row>
+    <row r="116" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A116" s="75"/>
+      <c r="B116" s="75"/>
       <c r="C116" s="4"/>
       <c r="D116" s="5"/>
       <c r="H116" s="5"/>
@@ -5514,9 +5516,9 @@
       <c r="X116" s="1"/>
       <c r="AA116" s="5"/>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A117" s="73"/>
-      <c r="B117" s="73"/>
+    <row r="117" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A117" s="75"/>
+      <c r="B117" s="75"/>
       <c r="C117" s="4"/>
       <c r="D117" s="5"/>
       <c r="H117" s="5"/>
@@ -5526,9 +5528,9 @@
       <c r="W117" s="1"/>
       <c r="AA117" s="5"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A118" s="73"/>
-      <c r="B118" s="73"/>
+    <row r="118" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A118" s="75"/>
+      <c r="B118" s="75"/>
       <c r="C118" s="4"/>
       <c r="D118" s="5"/>
       <c r="G118" s="3"/>
@@ -5539,65 +5541,65 @@
       <c r="V118" s="5"/>
       <c r="AA118" s="5"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A120" s="72"/>
-      <c r="B120" s="72"/>
-      <c r="C120" s="72"/>
-      <c r="D120" s="72"/>
-      <c r="E120" s="72"/>
-      <c r="F120" s="72"/>
-      <c r="G120" s="72"/>
-      <c r="H120" s="72"/>
-      <c r="I120" s="72"/>
-      <c r="J120" s="72"/>
-      <c r="K120" s="72"/>
-      <c r="L120" s="72"/>
-      <c r="M120" s="72"/>
-      <c r="N120" s="72"/>
-      <c r="O120" s="72"/>
-      <c r="P120" s="72"/>
-    </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A122" s="72"/>
-      <c r="B122" s="72"/>
-      <c r="C122" s="72"/>
-      <c r="D122" s="72"/>
-      <c r="E122" s="72"/>
-      <c r="F122" s="72"/>
-      <c r="G122" s="72"/>
-      <c r="H122" s="72"/>
-      <c r="I122" s="72"/>
-      <c r="J122" s="72"/>
-      <c r="K122" s="72"/>
-      <c r="L122" s="72"/>
-      <c r="M122" s="72"/>
-      <c r="N122" s="72"/>
-      <c r="O122" s="72"/>
-      <c r="P122" s="72"/>
-    </row>
-    <row r="123" spans="1:30" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="73"/>
-      <c r="B123" s="73"/>
-      <c r="E123" s="72"/>
-      <c r="F123" s="72"/>
-      <c r="G123" s="72"/>
+    <row r="120" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A120" s="74"/>
+      <c r="B120" s="74"/>
+      <c r="C120" s="74"/>
+      <c r="D120" s="74"/>
+      <c r="E120" s="74"/>
+      <c r="F120" s="74"/>
+      <c r="G120" s="74"/>
+      <c r="H120" s="74"/>
+      <c r="I120" s="74"/>
+      <c r="J120" s="74"/>
+      <c r="K120" s="74"/>
+      <c r="L120" s="74"/>
+      <c r="M120" s="74"/>
+      <c r="N120" s="74"/>
+      <c r="O120" s="74"/>
+      <c r="P120" s="74"/>
+    </row>
+    <row r="122" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A122" s="74"/>
+      <c r="B122" s="74"/>
+      <c r="C122" s="74"/>
+      <c r="D122" s="74"/>
+      <c r="E122" s="74"/>
+      <c r="F122" s="74"/>
+      <c r="G122" s="74"/>
+      <c r="H122" s="74"/>
+      <c r="I122" s="74"/>
+      <c r="J122" s="74"/>
+      <c r="K122" s="74"/>
+      <c r="L122" s="74"/>
+      <c r="M122" s="74"/>
+      <c r="N122" s="74"/>
+      <c r="O122" s="74"/>
+      <c r="P122" s="74"/>
+    </row>
+    <row r="123" spans="1:30" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="75"/>
+      <c r="B123" s="75"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="74"/>
       <c r="H123" s="5"/>
-      <c r="I123" s="72"/>
-      <c r="J123" s="72"/>
-      <c r="K123" s="72"/>
-      <c r="L123" s="72"/>
-      <c r="M123" s="72"/>
-      <c r="N123" s="72"/>
-      <c r="O123" s="72"/>
-      <c r="P123" s="72"/>
-    </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A124" s="73"/>
-      <c r="B124" s="73"/>
-    </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A125" s="73"/>
-      <c r="B125" s="73"/>
+      <c r="I123" s="74"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="74"/>
+      <c r="M123" s="74"/>
+      <c r="N123" s="74"/>
+      <c r="O123" s="74"/>
+      <c r="P123" s="74"/>
+    </row>
+    <row r="124" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A124" s="75"/>
+      <c r="B124" s="75"/>
+    </row>
+    <row r="125" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A125" s="75"/>
+      <c r="B125" s="75"/>
       <c r="C125" s="4"/>
       <c r="D125" s="5"/>
       <c r="H125" s="5"/>
@@ -5612,9 +5614,9 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A126" s="73"/>
-      <c r="B126" s="73"/>
+    <row r="126" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A126" s="75"/>
+      <c r="B126" s="75"/>
       <c r="C126" s="4"/>
       <c r="D126" s="5"/>
       <c r="E126" s="1"/>
@@ -5623,9 +5625,9 @@
       <c r="V126" s="5"/>
       <c r="AA126" s="5"/>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A127" s="73"/>
-      <c r="B127" s="73"/>
+    <row r="127" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A127" s="75"/>
+      <c r="B127" s="75"/>
       <c r="C127" s="4"/>
       <c r="D127" s="5"/>
       <c r="E127" s="1"/>
@@ -5640,47 +5642,47 @@
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" s="72"/>
-      <c r="B130" s="72"/>
-      <c r="C130" s="72"/>
-      <c r="D130" s="72"/>
-      <c r="E130" s="72"/>
-      <c r="F130" s="72"/>
-      <c r="G130" s="72"/>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" s="73"/>
-      <c r="B131" s="73"/>
-      <c r="E131" s="72"/>
-      <c r="F131" s="72"/>
-      <c r="G131" s="72"/>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A130" s="74"/>
+      <c r="B130" s="74"/>
+      <c r="C130" s="74"/>
+      <c r="D130" s="74"/>
+      <c r="E130" s="74"/>
+      <c r="F130" s="74"/>
+      <c r="G130" s="74"/>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A131" s="75"/>
+      <c r="B131" s="75"/>
+      <c r="E131" s="74"/>
+      <c r="F131" s="74"/>
+      <c r="G131" s="74"/>
       <c r="H131" s="5"/>
-      <c r="I131" s="72"/>
-      <c r="J131" s="72"/>
-      <c r="K131" s="72"/>
-      <c r="L131" s="72"/>
-      <c r="M131" s="72"/>
-      <c r="N131" s="72"/>
-      <c r="O131" s="72"/>
-      <c r="P131" s="72"/>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" s="73"/>
-      <c r="B132" s="73"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" s="73"/>
-      <c r="B133" s="73"/>
+      <c r="I131" s="74"/>
+      <c r="J131" s="74"/>
+      <c r="K131" s="74"/>
+      <c r="L131" s="74"/>
+      <c r="M131" s="74"/>
+      <c r="N131" s="74"/>
+      <c r="O131" s="74"/>
+      <c r="P131" s="74"/>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A132" s="75"/>
+      <c r="B132" s="75"/>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A133" s="75"/>
+      <c r="B133" s="75"/>
       <c r="C133" s="4"/>
       <c r="D133" s="5"/>
       <c r="G133" s="4"/>
       <c r="H133" s="5"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" s="73"/>
-      <c r="B134" s="73"/>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A134" s="75"/>
+      <c r="B134" s="75"/>
       <c r="C134" s="4"/>
       <c r="D134" s="5"/>
       <c r="G134" s="4"/>
@@ -5688,9 +5690,9 @@
       <c r="J134" s="1"/>
       <c r="M134" s="5"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" s="73"/>
-      <c r="B135" s="73"/>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A135" s="75"/>
+      <c r="B135" s="75"/>
       <c r="C135" s="4"/>
       <c r="D135" s="5"/>
       <c r="E135" s="2"/>
@@ -5698,131 +5700,89 @@
       <c r="H135" s="5"/>
       <c r="M135" s="5"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" s="72"/>
-      <c r="B138" s="72"/>
-      <c r="C138" s="72"/>
-      <c r="D138" s="72"/>
-      <c r="E138" s="72"/>
-      <c r="F138" s="72"/>
-      <c r="G138" s="72"/>
-      <c r="H138" s="72"/>
-      <c r="I138" s="72"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A139" s="73"/>
-      <c r="B139" s="73"/>
-      <c r="E139" s="72"/>
-      <c r="F139" s="72"/>
-      <c r="G139" s="72"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A140" s="73"/>
-      <c r="B140" s="73"/>
-      <c r="H140" s="74"/>
-      <c r="I140" s="74"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A141" s="73"/>
-      <c r="B141" s="73"/>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A138" s="74"/>
+      <c r="B138" s="74"/>
+      <c r="C138" s="74"/>
+      <c r="D138" s="74"/>
+      <c r="E138" s="74"/>
+      <c r="F138" s="74"/>
+      <c r="G138" s="74"/>
+      <c r="H138" s="74"/>
+      <c r="I138" s="74"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A139" s="75"/>
+      <c r="B139" s="75"/>
+      <c r="E139" s="74"/>
+      <c r="F139" s="74"/>
+      <c r="G139" s="74"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A140" s="75"/>
+      <c r="B140" s="75"/>
+      <c r="H140" s="76"/>
+      <c r="I140" s="76"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A141" s="75"/>
+      <c r="B141" s="75"/>
       <c r="C141" s="4"/>
       <c r="D141" s="5"/>
       <c r="G141" s="4"/>
-      <c r="H141" s="74"/>
-      <c r="I141" s="74"/>
-    </row>
-    <row r="142" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="73"/>
-      <c r="B142" s="73"/>
+      <c r="H141" s="76"/>
+      <c r="I141" s="76"/>
+    </row>
+    <row r="142" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="75"/>
+      <c r="B142" s="75"/>
       <c r="C142" s="4"/>
       <c r="D142" s="5"/>
       <c r="F142" s="6"/>
       <c r="G142" s="4"/>
-      <c r="H142" s="74"/>
-      <c r="I142" s="74"/>
-    </row>
-    <row r="143" spans="1:16" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="73"/>
-      <c r="B143" s="73"/>
+      <c r="H142" s="76"/>
+      <c r="I142" s="76"/>
+    </row>
+    <row r="143" spans="1:16" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="75"/>
+      <c r="B143" s="75"/>
       <c r="C143" s="4"/>
       <c r="D143" s="5"/>
       <c r="E143" s="3"/>
       <c r="F143" s="6"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="74"/>
-      <c r="I143" s="74"/>
+      <c r="H143" s="76"/>
+      <c r="I143" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="A1:P2"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="A19:P19"/>
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="A12:P12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A38:A42"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:P38"/>
-    <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="A54:P54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="I55:L55"/>
-    <mergeCell ref="M55:P55"/>
-    <mergeCell ref="A44:P44"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="A70:P70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="I71:L71"/>
-    <mergeCell ref="M71:P71"/>
-    <mergeCell ref="A62:P62"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="A86:P86"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="E87:G87"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="M87:P87"/>
-    <mergeCell ref="A78:P78"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="E79:G79"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="M79:P79"/>
+    <mergeCell ref="A138:I138"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="B139:B143"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="H140:I140"/>
+    <mergeCell ref="H141:I141"/>
+    <mergeCell ref="H142:I142"/>
+    <mergeCell ref="H143:I143"/>
+    <mergeCell ref="A130:G130"/>
+    <mergeCell ref="A131:A135"/>
+    <mergeCell ref="B131:B135"/>
+    <mergeCell ref="E131:G131"/>
+    <mergeCell ref="I131:L131"/>
+    <mergeCell ref="M131:P131"/>
+    <mergeCell ref="A120:P120"/>
+    <mergeCell ref="A122:P122"/>
+    <mergeCell ref="A123:A127"/>
+    <mergeCell ref="B123:B127"/>
+    <mergeCell ref="E123:G123"/>
+    <mergeCell ref="I123:L123"/>
+    <mergeCell ref="M123:P123"/>
+    <mergeCell ref="A113:P113"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="B114:B118"/>
+    <mergeCell ref="E114:G114"/>
+    <mergeCell ref="I114:L114"/>
+    <mergeCell ref="M114:P114"/>
     <mergeCell ref="A101:P101"/>
     <mergeCell ref="A103:P103"/>
     <mergeCell ref="A105:P105"/>
@@ -5837,33 +5797,75 @@
     <mergeCell ref="E95:G95"/>
     <mergeCell ref="I95:L95"/>
     <mergeCell ref="M95:P95"/>
-    <mergeCell ref="M131:P131"/>
-    <mergeCell ref="A120:P120"/>
-    <mergeCell ref="A122:P122"/>
-    <mergeCell ref="A123:A127"/>
-    <mergeCell ref="B123:B127"/>
-    <mergeCell ref="E123:G123"/>
-    <mergeCell ref="I123:L123"/>
-    <mergeCell ref="M123:P123"/>
-    <mergeCell ref="A113:P113"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="B114:B118"/>
-    <mergeCell ref="E114:G114"/>
-    <mergeCell ref="I114:L114"/>
-    <mergeCell ref="M114:P114"/>
-    <mergeCell ref="A138:I138"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="B139:B143"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="H140:I140"/>
-    <mergeCell ref="H141:I141"/>
-    <mergeCell ref="H142:I142"/>
-    <mergeCell ref="H143:I143"/>
-    <mergeCell ref="A130:G130"/>
-    <mergeCell ref="A131:A135"/>
-    <mergeCell ref="B131:B135"/>
-    <mergeCell ref="E131:G131"/>
-    <mergeCell ref="I131:L131"/>
+    <mergeCell ref="A86:P86"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="M87:P87"/>
+    <mergeCell ref="A78:P78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="M79:P79"/>
+    <mergeCell ref="A70:P70"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="M71:P71"/>
+    <mergeCell ref="A62:P62"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="A54:P54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="M55:P55"/>
+    <mergeCell ref="A44:P44"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="A29:P29"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="A12:P12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="A19:P19"/>
+    <mergeCell ref="A21:P21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
